--- a/section 2.xlsx
+++ b/section 2.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet state="visible" name="sc2_half" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="sc2_quarter" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="df_main" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3232" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3605" uniqueCount="100">
   <si>
     <t>Type</t>
   </si>
@@ -229,6 +230,90 @@
   <si>
     <t>USD mn</t>
   </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Assets</t>
+  </si>
+  <si>
+    <t>Direct Investment</t>
+  </si>
+  <si>
+    <t>Asia-Pacific</t>
+  </si>
+  <si>
+    <t>Portfolio Equity</t>
+  </si>
+  <si>
+    <t>Portfolio Debt</t>
+  </si>
+  <si>
+    <t>Financial Derivatives</t>
+  </si>
+  <si>
+    <t>Currency &amp; Deposits</t>
+  </si>
+  <si>
+    <t>Loans</t>
+  </si>
+  <si>
+    <t>Trade Credit &amp; Advances</t>
+  </si>
+  <si>
+    <t>Other Investments</t>
+  </si>
+  <si>
+    <t>Reserve Assets</t>
+  </si>
+  <si>
+    <t>Asia-Pacific Total</t>
+  </si>
+  <si>
+    <t>Asian Advance Economies</t>
+  </si>
+  <si>
+    <t>Asian Advance Economies Total</t>
+  </si>
+  <si>
+    <t>ASEAN5 Economies</t>
+  </si>
+  <si>
+    <t>ASEAN5 Economies Total</t>
+  </si>
+  <si>
+    <t>Asian EDMEs</t>
+  </si>
+  <si>
+    <t>Asian EDMEs Total</t>
+  </si>
+  <si>
+    <t>China Total</t>
+  </si>
+  <si>
+    <t>India Total</t>
+  </si>
+  <si>
+    <t>Liabilities</t>
+  </si>
+  <si>
+    <t>Current Account</t>
+  </si>
+  <si>
+    <t>Goods Trade</t>
+  </si>
+  <si>
+    <t>Services Trade</t>
+  </si>
+  <si>
+    <t>Primary Income</t>
+  </si>
+  <si>
+    <t>Secondary Income</t>
+  </si>
+  <si>
+    <t>Current Account Balance</t>
+  </si>
 </sst>
 </file>
 
@@ -290,6 +375,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -69249,4 +69338,6016 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="2">
+        <v>149.4281495189</v>
+      </c>
+      <c r="E2" s="2">
+        <v>180.51055453707</v>
+      </c>
+      <c r="F2" s="2">
+        <v>180.62047046682</v>
+      </c>
+      <c r="G2" s="2">
+        <v>185.83368608806998</v>
+      </c>
+      <c r="H2" s="2">
+        <v>225.41143097134</v>
+      </c>
+      <c r="I2" s="2">
+        <v>243.14716296758002</v>
+      </c>
+      <c r="J2" s="2">
+        <v>273.81568658835</v>
+      </c>
+      <c r="K2" s="2">
+        <v>238.8980662714</v>
+      </c>
+      <c r="L2" s="2">
+        <v>224.55279877550998</v>
+      </c>
+      <c r="M2" s="2">
+        <v>231.25916708451</v>
+      </c>
+      <c r="N2" s="2">
+        <v>241.25090282489998</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="2">
+        <v>69.7087628454409</v>
+      </c>
+      <c r="E3" s="2">
+        <v>90.8287453568382</v>
+      </c>
+      <c r="F3" s="2">
+        <v>90.13388484327271</v>
+      </c>
+      <c r="G3" s="2">
+        <v>203.79963449788121</v>
+      </c>
+      <c r="H3" s="2">
+        <v>220.5658849116192</v>
+      </c>
+      <c r="I3" s="2">
+        <v>114.62735206816559</v>
+      </c>
+      <c r="J3" s="2">
+        <v>100.8838615232268</v>
+      </c>
+      <c r="K3" s="2">
+        <v>79.48838875000631</v>
+      </c>
+      <c r="L3" s="2">
+        <v>83.9485917861433</v>
+      </c>
+      <c r="M3" s="2">
+        <v>96.05344267818359</v>
+      </c>
+      <c r="N3" s="2">
+        <v>184.6128585630249</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="2">
+        <v>141.7318813893791</v>
+      </c>
+      <c r="E4" s="2">
+        <v>66.6389447583218</v>
+      </c>
+      <c r="F4" s="2">
+        <v>53.630082243097306</v>
+      </c>
+      <c r="G4" s="2">
+        <v>35.3421252795888</v>
+      </c>
+      <c r="H4" s="2">
+        <v>75.6107338107808</v>
+      </c>
+      <c r="I4" s="2">
+        <v>81.5954911204244</v>
+      </c>
+      <c r="J4" s="2">
+        <v>128.0513276394332</v>
+      </c>
+      <c r="K4" s="2">
+        <v>122.46262231798369</v>
+      </c>
+      <c r="L4" s="2">
+        <v>125.5568445032767</v>
+      </c>
+      <c r="M4" s="2">
+        <v>65.3340809801764</v>
+      </c>
+      <c r="N4" s="2">
+        <v>193.6878658027851</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="2">
+        <v>-30.79185735964</v>
+      </c>
+      <c r="E5" s="2">
+        <v>-19.369327982869997</v>
+      </c>
+      <c r="F5" s="2">
+        <v>-31.317722517630003</v>
+      </c>
+      <c r="G5" s="2">
+        <v>-28.782652446810005</v>
+      </c>
+      <c r="H5" s="2">
+        <v>-58.157658105989995</v>
+      </c>
+      <c r="I5" s="2">
+        <v>-33.88665397724</v>
+      </c>
+      <c r="J5" s="2">
+        <v>-26.049554997869997</v>
+      </c>
+      <c r="K5" s="2">
+        <v>-67.2629775225</v>
+      </c>
+      <c r="L5" s="2">
+        <v>-17.17122925215</v>
+      </c>
+      <c r="M5" s="2">
+        <v>-53.29422865946</v>
+      </c>
+      <c r="N5" s="2">
+        <v>-32.694167342179995</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3.800398086030012</v>
+      </c>
+      <c r="E6" s="2">
+        <v>159.859280604395</v>
+      </c>
+      <c r="F6" s="2">
+        <v>115.000414582395</v>
+      </c>
+      <c r="G6" s="2">
+        <v>181.996993398425</v>
+      </c>
+      <c r="H6" s="2">
+        <v>163.467292107975</v>
+      </c>
+      <c r="I6" s="2">
+        <v>166.64597267348</v>
+      </c>
+      <c r="J6" s="2">
+        <v>129.16144655955998</v>
+      </c>
+      <c r="K6" s="2">
+        <v>61.908016056860006</v>
+      </c>
+      <c r="L6" s="2">
+        <v>-50.352413726650006</v>
+      </c>
+      <c r="M6" s="2">
+        <v>158.941184662085</v>
+      </c>
+      <c r="N6" s="2">
+        <v>17.39766807601999</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="2">
+        <v>33.95205834435679</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-4.4653259222335056</v>
+      </c>
+      <c r="F7" s="2">
+        <v>104.59701641697811</v>
+      </c>
+      <c r="G7" s="2">
+        <v>68.41182395583671</v>
+      </c>
+      <c r="H7" s="2">
+        <v>175.25118268395747</v>
+      </c>
+      <c r="I7" s="2">
+        <v>25.547410508434798</v>
+      </c>
+      <c r="J7" s="2">
+        <v>25.360590974033194</v>
+      </c>
+      <c r="K7" s="2">
+        <v>-70.19942430199679</v>
+      </c>
+      <c r="L7" s="2">
+        <v>-44.0197781253942</v>
+      </c>
+      <c r="M7" s="2">
+        <v>-13.845784355736498</v>
+      </c>
+      <c r="N7" s="2">
+        <v>4.073932539714798</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="2">
+        <v>-64.7194181166672</v>
+      </c>
+      <c r="E8" s="2">
+        <v>28.066665881256498</v>
+      </c>
+      <c r="F8" s="2">
+        <v>-40.9193984517299</v>
+      </c>
+      <c r="G8" s="2">
+        <v>78.27755431874071</v>
+      </c>
+      <c r="H8" s="2">
+        <v>16.5810974453975</v>
+      </c>
+      <c r="I8" s="2">
+        <v>80.93755284542081</v>
+      </c>
+      <c r="J8" s="2">
+        <v>-9.041628215482806</v>
+      </c>
+      <c r="K8" s="2">
+        <v>14.255986203297201</v>
+      </c>
+      <c r="L8" s="2">
+        <v>-26.0716273294282</v>
+      </c>
+      <c r="M8" s="2">
+        <v>55.4597934750635</v>
+      </c>
+      <c r="N8" s="2">
+        <v>9.270943204260803</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="2">
+        <v>37.4628464472804</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-1.3411633487980001</v>
+      </c>
+      <c r="F9" s="2">
+        <v>51.7353804691868</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1.634338903897599</v>
+      </c>
+      <c r="H9" s="2">
+        <v>67.38836202918999</v>
+      </c>
+      <c r="I9" s="2">
+        <v>32.3535555670944</v>
+      </c>
+      <c r="J9" s="2">
+        <v>68.6713557408796</v>
+      </c>
+      <c r="K9" s="2">
+        <v>-29.5524334667204</v>
+      </c>
+      <c r="L9" s="2">
+        <v>36.085603051742396</v>
+      </c>
+      <c r="M9" s="2">
+        <v>-2.2311250520819996</v>
+      </c>
+      <c r="N9" s="2">
+        <v>50.9521395365644</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="2">
+        <v>48.47186965067</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46.623625435520005</v>
+      </c>
+      <c r="F10" s="2">
+        <v>105.03012423234</v>
+      </c>
+      <c r="G10" s="2">
+        <v>252.3874904511</v>
+      </c>
+      <c r="H10" s="2">
+        <v>179.18483768391</v>
+      </c>
+      <c r="I10" s="2">
+        <v>205.65166769023</v>
+      </c>
+      <c r="J10" s="2">
+        <v>-131.59235543398998</v>
+      </c>
+      <c r="K10" s="2">
+        <v>-5.5088949529599915</v>
+      </c>
+      <c r="L10" s="2">
+        <v>110.46451448298001</v>
+      </c>
+      <c r="M10" s="2">
+        <v>15.00170221288</v>
+      </c>
+      <c r="N10" s="2">
+        <v>37.612147287730004</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="2">
+        <v>389.04469080575</v>
+      </c>
+      <c r="E11" s="2">
+        <v>547.3519993195</v>
+      </c>
+      <c r="F11" s="2">
+        <v>628.5102522847301</v>
+      </c>
+      <c r="G11" s="2">
+        <v>978.90099444673</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1065.30316353818</v>
+      </c>
+      <c r="I11" s="2">
+        <v>916.61951146359</v>
+      </c>
+      <c r="J11" s="2">
+        <v>559.2607303781399</v>
+      </c>
+      <c r="K11" s="2">
+        <v>344.48934935537005</v>
+      </c>
+      <c r="L11" s="2">
+        <v>442.99330416602993</v>
+      </c>
+      <c r="M11" s="2">
+        <v>552.67823302562</v>
+      </c>
+      <c r="N11" s="2">
+        <v>706.1642904928201</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="2">
+        <v>60.62845954772</v>
+      </c>
+      <c r="E12" s="2">
+        <v>91.87520880528</v>
+      </c>
+      <c r="F12" s="2">
+        <v>84.03621911317</v>
+      </c>
+      <c r="G12" s="2">
+        <v>85.55940775090001</v>
+      </c>
+      <c r="H12" s="2">
+        <v>118.54381562361999</v>
+      </c>
+      <c r="I12" s="2">
+        <v>113.56537811044001</v>
+      </c>
+      <c r="J12" s="2">
+        <v>158.2872821854</v>
+      </c>
+      <c r="K12" s="2">
+        <v>94.35908023593</v>
+      </c>
+      <c r="L12" s="2">
+        <v>114.77078044512</v>
+      </c>
+      <c r="M12" s="2">
+        <v>110.17897134915</v>
+      </c>
+      <c r="N12" s="2">
+        <v>105.85709895240001</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="2">
+        <v>59.52457782214089</v>
+      </c>
+      <c r="E13" s="2">
+        <v>56.6838271187782</v>
+      </c>
+      <c r="F13" s="2">
+        <v>39.0172469395127</v>
+      </c>
+      <c r="G13" s="2">
+        <v>95.7333270441212</v>
+      </c>
+      <c r="H13" s="2">
+        <v>124.6298766970492</v>
+      </c>
+      <c r="I13" s="2">
+        <v>94.3784353339056</v>
+      </c>
+      <c r="J13" s="2">
+        <v>72.2883118980068</v>
+      </c>
+      <c r="K13" s="2">
+        <v>53.4599895155663</v>
+      </c>
+      <c r="L13" s="2">
+        <v>53.8793885149033</v>
+      </c>
+      <c r="M13" s="2">
+        <v>62.0624044440836</v>
+      </c>
+      <c r="N13" s="2">
+        <v>112.0301948310849</v>
+      </c>
+      <c r="O13" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="2">
+        <v>105.7070039115291</v>
+      </c>
+      <c r="E14" s="2">
+        <v>34.2115594550718</v>
+      </c>
+      <c r="F14" s="2">
+        <v>37.1990975789073</v>
+      </c>
+      <c r="G14" s="2">
+        <v>31.3122030202788</v>
+      </c>
+      <c r="H14" s="2">
+        <v>43.3139354080008</v>
+      </c>
+      <c r="I14" s="2">
+        <v>66.9429040024244</v>
+      </c>
+      <c r="J14" s="2">
+        <v>64.3942353669532</v>
+      </c>
+      <c r="K14" s="2">
+        <v>45.01097939610369</v>
+      </c>
+      <c r="L14" s="2">
+        <v>90.36268323089669</v>
+      </c>
+      <c r="M14" s="2">
+        <v>66.1259944188664</v>
+      </c>
+      <c r="N14" s="2">
+        <v>149.4726420864551</v>
+      </c>
+      <c r="O14" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="2">
+        <v>-36.00768287174</v>
+      </c>
+      <c r="E15" s="2">
+        <v>-30.680472440819997</v>
+      </c>
+      <c r="F15" s="2">
+        <v>-46.48902021467</v>
+      </c>
+      <c r="G15" s="2">
+        <v>-31.36048445438</v>
+      </c>
+      <c r="H15" s="2">
+        <v>-54.68703175569</v>
+      </c>
+      <c r="I15" s="2">
+        <v>-35.23260410406</v>
+      </c>
+      <c r="J15" s="2">
+        <v>-43.98563499166</v>
+      </c>
+      <c r="K15" s="2">
+        <v>-70.78013838201</v>
+      </c>
+      <c r="L15" s="2">
+        <v>-26.28750622911</v>
+      </c>
+      <c r="M15" s="2">
+        <v>-66.1549869337</v>
+      </c>
+      <c r="N15" s="2">
+        <v>-51.58841598881</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="2">
+        <v>-87.61593239516999</v>
+      </c>
+      <c r="E16" s="2">
+        <v>79.620259410405</v>
+      </c>
+      <c r="F16" s="2">
+        <v>47.033614911404996</v>
+      </c>
+      <c r="G16" s="2">
+        <v>50.177864693655</v>
+      </c>
+      <c r="H16" s="2">
+        <v>57.107752256785</v>
+      </c>
+      <c r="I16" s="2">
+        <v>63.587816709100004</v>
+      </c>
+      <c r="J16" s="2">
+        <v>114.32452914301999</v>
+      </c>
+      <c r="K16" s="2">
+        <v>15.048641504730007</v>
+      </c>
+      <c r="L16" s="2">
+        <v>-46.77700993996</v>
+      </c>
+      <c r="M16" s="2">
+        <v>95.46343062174499</v>
+      </c>
+      <c r="N16" s="2">
+        <v>-4.5009942548499975</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="2">
+        <v>35.5853930916668</v>
+      </c>
+      <c r="E17" s="2">
+        <v>18.3674544405865</v>
+      </c>
+      <c r="F17" s="2">
+        <v>37.6562136839081</v>
+      </c>
+      <c r="G17" s="2">
+        <v>-4.511296302003299</v>
+      </c>
+      <c r="H17" s="2">
+        <v>22.7931877176975</v>
+      </c>
+      <c r="I17" s="2">
+        <v>35.3956431428948</v>
+      </c>
+      <c r="J17" s="2">
+        <v>39.7966479555632</v>
+      </c>
+      <c r="K17" s="2">
+        <v>23.8052767046232</v>
+      </c>
+      <c r="L17" s="2">
+        <v>-33.3050858934742</v>
+      </c>
+      <c r="M17" s="2">
+        <v>5.6516270077935</v>
+      </c>
+      <c r="N17" s="2">
+        <v>-13.4718449862252</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="2">
+        <v>-6.8954372639572</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3.6770236579564997</v>
+      </c>
+      <c r="F18" s="2">
+        <v>-5.928063312169901</v>
+      </c>
+      <c r="G18" s="2">
+        <v>5.869586638280699</v>
+      </c>
+      <c r="H18" s="2">
+        <v>11.9425895715875</v>
+      </c>
+      <c r="I18" s="2">
+        <v>15.3879839251508</v>
+      </c>
+      <c r="J18" s="2">
+        <v>8.002761989407198</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0.7837085419572004</v>
+      </c>
+      <c r="L18" s="2">
+        <v>-7.288696598948201</v>
+      </c>
+      <c r="M18" s="2">
+        <v>18.1512336086635</v>
+      </c>
+      <c r="N18" s="2">
+        <v>5.332202084550801</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="2">
+        <v>7.4072962231504</v>
+      </c>
+      <c r="E19" s="2">
+        <v>-5.992089741938001</v>
+      </c>
+      <c r="F19" s="2">
+        <v>20.9457718952768</v>
+      </c>
+      <c r="G19" s="2">
+        <v>-12.2548098254124</v>
+      </c>
+      <c r="H19" s="2">
+        <v>18.6025987843</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1.9987241851544018</v>
+      </c>
+      <c r="J19" s="2">
+        <v>43.0398085306796</v>
+      </c>
+      <c r="K19" s="2">
+        <v>-21.348410036760402</v>
+      </c>
+      <c r="L19" s="2">
+        <v>10.4991004632824</v>
+      </c>
+      <c r="M19" s="2">
+        <v>-4.141101501982</v>
+      </c>
+      <c r="N19" s="2">
+        <v>27.3866266979544</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="2">
+        <v>-3.82404573347</v>
+      </c>
+      <c r="E20" s="2">
+        <v>12.441865295869999</v>
+      </c>
+      <c r="F20" s="2">
+        <v>50.28459618136</v>
+      </c>
+      <c r="G20" s="2">
+        <v>124.1705343534</v>
+      </c>
+      <c r="H20" s="2">
+        <v>58.42038928782</v>
+      </c>
+      <c r="I20" s="2">
+        <v>42.57743607367001</v>
+      </c>
+      <c r="J20" s="2">
+        <v>-127.06030114248999</v>
+      </c>
+      <c r="K20" s="2">
+        <v>-51.37918509766</v>
+      </c>
+      <c r="L20" s="2">
+        <v>39.84381088862</v>
+      </c>
+      <c r="M20" s="2">
+        <v>21.805583308870002</v>
+      </c>
+      <c r="N20" s="2">
+        <v>11.6767359212</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" s="2">
+        <v>134.50963233187</v>
+      </c>
+      <c r="E21" s="2">
+        <v>260.20463600119</v>
+      </c>
+      <c r="F21" s="2">
+        <v>263.7556767767</v>
+      </c>
+      <c r="G21" s="2">
+        <v>344.69633291884</v>
+      </c>
+      <c r="H21" s="2">
+        <v>400.66711359117</v>
+      </c>
+      <c r="I21" s="2">
+        <v>398.60171737868</v>
+      </c>
+      <c r="J21" s="2">
+        <v>329.08764093487997</v>
+      </c>
+      <c r="K21" s="2">
+        <v>88.95994238248</v>
+      </c>
+      <c r="L21" s="2">
+        <v>195.69746488132998</v>
+      </c>
+      <c r="M21" s="2">
+        <v>309.14315632348996</v>
+      </c>
+      <c r="N21" s="2">
+        <v>342.19424534376003</v>
+      </c>
+      <c r="O21" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P21" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="2">
+        <v>14.812851098289999</v>
+      </c>
+      <c r="E22" s="2">
+        <v>11.17706201338</v>
+      </c>
+      <c r="F22" s="2">
+        <v>13.842823974529999</v>
+      </c>
+      <c r="G22" s="2">
+        <v>17.03391524292</v>
+      </c>
+      <c r="H22" s="2">
+        <v>13.32269309508</v>
+      </c>
+      <c r="I22" s="2">
+        <v>25.36892558712</v>
+      </c>
+      <c r="J22" s="2">
+        <v>12.19136114016</v>
+      </c>
+      <c r="K22" s="2">
+        <v>20.59560221418</v>
+      </c>
+      <c r="L22" s="2">
+        <v>15.51801934032</v>
+      </c>
+      <c r="M22" s="2">
+        <v>15.57959446987</v>
+      </c>
+      <c r="N22" s="2">
+        <v>16.893682833899998</v>
+      </c>
+      <c r="O22" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P22" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="2">
+        <v>2.5588293984600003</v>
+      </c>
+      <c r="E23" s="2">
+        <v>10.26737808985</v>
+      </c>
+      <c r="F23" s="2">
+        <v>6.04544905754</v>
+      </c>
+      <c r="G23" s="2">
+        <v>21.49401910494</v>
+      </c>
+      <c r="H23" s="2">
+        <v>22.46332650761</v>
+      </c>
+      <c r="I23" s="2">
+        <v>6.22770471946</v>
+      </c>
+      <c r="J23" s="2">
+        <v>2.4482615058799997</v>
+      </c>
+      <c r="K23" s="2">
+        <v>3.2869117185400003</v>
+      </c>
+      <c r="L23" s="2">
+        <v>7.91855024915</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0.3757574053499999</v>
+      </c>
+      <c r="N23" s="2">
+        <v>9.14644889301</v>
+      </c>
+      <c r="O23" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P23" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2.19599550889</v>
+      </c>
+      <c r="E24" s="2">
+        <v>6.12769129956</v>
+      </c>
+      <c r="F24" s="2">
+        <v>-2.78142363043</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1.6206845086200001</v>
+      </c>
+      <c r="H24" s="2">
+        <v>5.1430880532</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1.2672662858</v>
+      </c>
+      <c r="J24" s="2">
+        <v>4.46969401654</v>
+      </c>
+      <c r="K24" s="2">
+        <v>3.9543918606700004</v>
+      </c>
+      <c r="L24" s="2">
+        <v>4.16823657435</v>
+      </c>
+      <c r="M24" s="2">
+        <v>7.64607208965</v>
+      </c>
+      <c r="N24" s="2">
+        <v>10.69416472879</v>
+      </c>
+      <c r="O24" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P24" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="2">
+        <v>-3.95965363526</v>
+      </c>
+      <c r="E25" s="2">
+        <v>-3.32036665379</v>
+      </c>
+      <c r="F25" s="2">
+        <v>-4.51742558444</v>
+      </c>
+      <c r="G25" s="2">
+        <v>-3.6439697634600003</v>
+      </c>
+      <c r="H25" s="2">
+        <v>-3.6962069306400003</v>
+      </c>
+      <c r="I25" s="2">
+        <v>-3.6742774925899995</v>
+      </c>
+      <c r="J25" s="2">
+        <v>-5.01803287206</v>
+      </c>
+      <c r="K25" s="2">
+        <v>-6.189965700609999</v>
+      </c>
+      <c r="L25" s="2">
+        <v>-5.39520338901</v>
+      </c>
+      <c r="M25" s="2">
+        <v>-4.828646390069999</v>
+      </c>
+      <c r="N25" s="2">
+        <v>-5.66211819794</v>
+      </c>
+      <c r="O25" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P25" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="2">
+        <v>15.86064155618</v>
+      </c>
+      <c r="E26" s="2">
+        <v>5.9773638733</v>
+      </c>
+      <c r="F26" s="2">
+        <v>7.96074515006</v>
+      </c>
+      <c r="G26" s="2">
+        <v>-0.6814298659199993</v>
+      </c>
+      <c r="H26" s="2">
+        <v>1.5498964403899995</v>
+      </c>
+      <c r="I26" s="2">
+        <v>5.28120874684</v>
+      </c>
+      <c r="J26" s="2">
+        <v>4.30691969727</v>
+      </c>
+      <c r="K26" s="2">
+        <v>17.318578431</v>
+      </c>
+      <c r="L26" s="2">
+        <v>-4.75215298972</v>
+      </c>
+      <c r="M26" s="2">
+        <v>13.83794147499</v>
+      </c>
+      <c r="N26" s="2">
+        <v>5.79490153679</v>
+      </c>
+      <c r="O26" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P26" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2.01349342277</v>
+      </c>
+      <c r="E27" s="2">
+        <v>-0.45983890725</v>
+      </c>
+      <c r="F27" s="2">
+        <v>6.23282738444</v>
+      </c>
+      <c r="G27" s="2">
+        <v>-1.2467685934999997</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0.7188070591799999</v>
+      </c>
+      <c r="I27" s="2">
+        <v>2.40077483501</v>
+      </c>
+      <c r="J27" s="2">
+        <v>2.3988237285199996</v>
+      </c>
+      <c r="K27" s="2">
+        <v>5.88999835271</v>
+      </c>
+      <c r="L27" s="2">
+        <v>1.37666303725</v>
+      </c>
+      <c r="M27" s="2">
+        <v>2.99595895369</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0.9840611705899996</v>
+      </c>
+      <c r="O27" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P27" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2.6437113154299996</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2.02410164639</v>
+      </c>
+      <c r="F28" s="2">
+        <v>-3.6874858976700002</v>
+      </c>
+      <c r="G28" s="2">
+        <v>4.43038688657</v>
+      </c>
+      <c r="H28" s="2">
+        <v>-0.08414967364999981</v>
+      </c>
+      <c r="I28" s="2">
+        <v>7.8491202466</v>
+      </c>
+      <c r="J28" s="2">
+        <v>7.24253004591</v>
+      </c>
+      <c r="K28" s="2">
+        <v>-1.6003111415599998</v>
+      </c>
+      <c r="L28" s="2">
+        <v>6.82458837205</v>
+      </c>
+      <c r="M28" s="2">
+        <v>-1.0102577853899999</v>
+      </c>
+      <c r="N28" s="2">
+        <v>-3.5590323139199995</v>
+      </c>
+      <c r="O28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P28" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1.1147999178599999</v>
+      </c>
+      <c r="E29" s="2">
+        <v>3.5357272362799996</v>
+      </c>
+      <c r="F29" s="2">
+        <v>3.23368482815</v>
+      </c>
+      <c r="G29" s="2">
+        <v>3.26437003022</v>
+      </c>
+      <c r="H29" s="2">
+        <v>3.52741365015</v>
+      </c>
+      <c r="I29" s="2">
+        <v>-0.08930200145</v>
+      </c>
+      <c r="J29" s="2">
+        <v>3.16396865359</v>
+      </c>
+      <c r="K29" s="2">
+        <v>3.3960379293200003</v>
+      </c>
+      <c r="L29" s="2">
+        <v>-7.125507386810001</v>
+      </c>
+      <c r="M29" s="2">
+        <v>1.16353376126</v>
+      </c>
+      <c r="N29" s="2">
+        <v>0.98143589645</v>
+      </c>
+      <c r="O29" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P29" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="2">
+        <v>18.924110503420003</v>
+      </c>
+      <c r="E30" s="2">
+        <v>28.38826347733</v>
+      </c>
+      <c r="F30" s="2">
+        <v>21.82557630369</v>
+      </c>
+      <c r="G30" s="2">
+        <v>27.20206781553</v>
+      </c>
+      <c r="H30" s="2">
+        <v>3.426075805559999</v>
+      </c>
+      <c r="I30" s="2">
+        <v>29.613540054190004</v>
+      </c>
+      <c r="J30" s="2">
+        <v>-11.65512402565</v>
+      </c>
+      <c r="K30" s="2">
+        <v>-12.539342989279998</v>
+      </c>
+      <c r="L30" s="2">
+        <v>1.3106319293100004</v>
+      </c>
+      <c r="M30" s="2">
+        <v>12.31473366975</v>
+      </c>
+      <c r="N30" s="2">
+        <v>-6.9956453736999995</v>
+      </c>
+      <c r="O30" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P30" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="2">
+        <v>56.16477908604</v>
+      </c>
+      <c r="E31" s="2">
+        <v>63.71738207505</v>
+      </c>
+      <c r="F31" s="2">
+        <v>48.154771585869995</v>
+      </c>
+      <c r="G31" s="2">
+        <v>69.47327536592</v>
+      </c>
+      <c r="H31" s="2">
+        <v>46.370944006879995</v>
+      </c>
+      <c r="I31" s="2">
+        <v>74.24496098098001</v>
+      </c>
+      <c r="J31" s="2">
+        <v>19.54840189016</v>
+      </c>
+      <c r="K31" s="2">
+        <v>34.11190067497</v>
+      </c>
+      <c r="L31" s="2">
+        <v>19.84382573689</v>
+      </c>
+      <c r="M31" s="2">
+        <v>48.07468764909999</v>
+      </c>
+      <c r="N31" s="2">
+        <v>28.277899173969995</v>
+      </c>
+      <c r="O31" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P31" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1.07811672394</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.31630383579</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.7956674300600001</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0.34264710165</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0.23996935945</v>
+      </c>
+      <c r="I32" s="2">
+        <v>1.4813377408799997</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0.97845994827</v>
+      </c>
+      <c r="K32" s="2">
+        <v>1.71955665854</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0.11413275488999995</v>
+      </c>
+      <c r="M32" s="2">
+        <v>0.47045074263</v>
+      </c>
+      <c r="N32" s="2">
+        <v>0.06985870476</v>
+      </c>
+      <c r="O32" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P32" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0.00564308697</v>
+      </c>
+      <c r="E33" s="2">
+        <v>-0.014491349430000001</v>
+      </c>
+      <c r="F33" s="2">
+        <v>-0.63247892285</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0.21136396305</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0.0570626841</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0.0153649758</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0.15700854661</v>
+      </c>
+      <c r="K33" s="2">
+        <v>0.04212952398</v>
+      </c>
+      <c r="L33" s="2">
+        <v>0.02649437769</v>
+      </c>
+      <c r="M33" s="2">
+        <v>0.11164767034</v>
+      </c>
+      <c r="N33" s="2">
+        <v>-0.00713885543</v>
+      </c>
+      <c r="O33" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P33" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0.09370619938</v>
+      </c>
+      <c r="E34" s="2">
+        <v>-0.05174518123999999</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1.59747786283</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0.17184044195000003</v>
+      </c>
+      <c r="H34" s="2">
+        <v>0.00198103948</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0.006774958520000001</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0.04456087136</v>
+      </c>
+      <c r="K34" s="2">
+        <v>0.08236460602</v>
+      </c>
+      <c r="L34" s="2">
+        <v>0.29686100913</v>
+      </c>
+      <c r="M34" s="2">
+        <v>0.18424485584</v>
+      </c>
+      <c r="N34" s="2">
+        <v>-0.04998615987000002</v>
+      </c>
+      <c r="O34" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="2">
+        <v>6.27E-6</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="J35" s="2">
+        <v>-0.01104992305</v>
+      </c>
+      <c r="K35" s="2">
+        <v>3.4774142000000005E-4</v>
+      </c>
+      <c r="L35" s="2">
+        <v>-0.00162321982</v>
+      </c>
+      <c r="M35" s="2">
+        <v>-0.00113141573</v>
+      </c>
+      <c r="N35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P35" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.6160190088199999</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2.3277772325100003</v>
+      </c>
+      <c r="F36" s="2">
+        <v>1.8743245972300002</v>
+      </c>
+      <c r="G36" s="2">
+        <v>2.3158076602100004</v>
+      </c>
+      <c r="H36" s="2">
+        <v>-3.0000122417800004</v>
+      </c>
+      <c r="I36" s="2">
+        <v>-1.53461924947</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0.39379515675000004</v>
+      </c>
+      <c r="K36" s="2">
+        <v>0.4442295609399999</v>
+      </c>
+      <c r="L36" s="2">
+        <v>1.32584752044</v>
+      </c>
+      <c r="M36" s="2">
+        <v>3.62258473278</v>
+      </c>
+      <c r="N36" s="2">
+        <v>2.76874722953</v>
+      </c>
+      <c r="O36" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P36" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0.5648095894</v>
+      </c>
+      <c r="E37" s="2">
+        <v>-0.07797117599999999</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.22082422929</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0.02702091715</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0.0030061878999999986</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0.22326885116</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0.009941012290000004</v>
+      </c>
+      <c r="K37" s="2">
+        <v>0.09252133878</v>
+      </c>
+      <c r="L37" s="2">
+        <v>0.03814469267000001</v>
+      </c>
+      <c r="M37" s="2">
+        <v>-0.29370318955</v>
+      </c>
+      <c r="N37" s="2">
+        <v>0.32811826473999994</v>
+      </c>
+      <c r="O37" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P37" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="2">
+        <v>-1.4676921681400001</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0.16554057691000001</v>
+      </c>
+      <c r="F38" s="2">
+        <v>-0.10362752813999998</v>
+      </c>
+      <c r="G38" s="2">
+        <v>-0.33870242989</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0.56022040266</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0.7771522275</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0.15001605261</v>
+      </c>
+      <c r="K38" s="2">
+        <v>0.7450525531099998</v>
+      </c>
+      <c r="L38" s="2">
+        <v>0.9122632966700001</v>
+      </c>
+      <c r="M38" s="2">
+        <v>1.14913838423</v>
+      </c>
+      <c r="N38" s="2">
+        <v>0.06884820609999999</v>
+      </c>
+      <c r="O38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P38" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0.033297283179999984</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0.26181411824999995</v>
+      </c>
+      <c r="F39" s="2">
+        <v>0.54308924855</v>
+      </c>
+      <c r="G39" s="2">
+        <v>-0.16213184385</v>
+      </c>
+      <c r="H39" s="2">
+        <v>-0.004832702850000006</v>
+      </c>
+      <c r="I39" s="2">
+        <v>-0.16385497977999997</v>
+      </c>
+      <c r="J39" s="2">
+        <v>0.19585226632000002</v>
+      </c>
+      <c r="K39" s="2">
+        <v>0.32018681484</v>
+      </c>
+      <c r="L39" s="2">
+        <v>0.5486330527600001</v>
+      </c>
+      <c r="M39" s="2">
+        <v>0.17967096365</v>
+      </c>
+      <c r="N39" s="2">
+        <v>7.967950999999999E-5</v>
+      </c>
+      <c r="O39" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P39" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2.82357055758</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.7663768360800001</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0.3238944869600002</v>
+      </c>
+      <c r="G40" s="2">
+        <v>2.0687232671099998</v>
+      </c>
+      <c r="H40" s="2">
+        <v>-2.58424973761</v>
+      </c>
+      <c r="I40" s="2">
+        <v>-1.75610996696</v>
+      </c>
+      <c r="J40" s="2">
+        <v>-1.79972507789</v>
+      </c>
+      <c r="K40" s="2">
+        <v>1.6349115405899999</v>
+      </c>
+      <c r="L40" s="2">
+        <v>3.93117583568</v>
+      </c>
+      <c r="M40" s="2">
+        <v>2.9063554098899997</v>
+      </c>
+      <c r="N40" s="2">
+        <v>1.43793310796</v>
+      </c>
+      <c r="O40" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P40" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="2">
+        <v>3.7474702811299996</v>
+      </c>
+      <c r="E41" s="2">
+        <v>3.6936048928700003</v>
+      </c>
+      <c r="F41" s="2">
+        <v>4.61917140393</v>
+      </c>
+      <c r="G41" s="2">
+        <v>4.63656907738</v>
+      </c>
+      <c r="H41" s="2">
+        <v>-4.72684873865</v>
+      </c>
+      <c r="I41" s="2">
+        <v>-0.9506854423500002</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0.11885885327000006</v>
+      </c>
+      <c r="K41" s="2">
+        <v>5.081300338219999</v>
+      </c>
+      <c r="L41" s="2">
+        <v>7.191929320109999</v>
+      </c>
+      <c r="M41" s="2">
+        <v>8.32925815408</v>
+      </c>
+      <c r="N41" s="2">
+        <v>4.6164601773</v>
+      </c>
+      <c r="O41" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P41" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="2">
+        <v>66.33704677792</v>
+      </c>
+      <c r="E42" s="2">
+        <v>70.57295322208</v>
+      </c>
+      <c r="F42" s="2">
+        <v>76.09006698485999</v>
+      </c>
+      <c r="G42" s="2">
+        <v>77.63074135324999</v>
+      </c>
+      <c r="H42" s="2">
+        <v>84.54991992334</v>
+      </c>
+      <c r="I42" s="2">
+        <v>94.24782005954</v>
+      </c>
+      <c r="J42" s="2">
+        <v>96.01154535329</v>
+      </c>
+      <c r="K42" s="2">
+        <v>114.03861540574</v>
+      </c>
+      <c r="L42" s="2">
+        <v>88.55108080448998</v>
+      </c>
+      <c r="M42" s="2">
+        <v>96.75036917674001</v>
+      </c>
+      <c r="N42" s="2">
+        <v>108.86476543075999</v>
+      </c>
+      <c r="O42" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P42" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="2">
+        <v>5.27318369303</v>
+      </c>
+      <c r="E43" s="2">
+        <v>24.059051311479998</v>
+      </c>
+      <c r="F43" s="2">
+        <v>46.245632795830005</v>
+      </c>
+      <c r="G43" s="2">
+        <v>85.13756317514</v>
+      </c>
+      <c r="H43" s="2">
+        <v>72.53026732847</v>
+      </c>
+      <c r="I43" s="2">
+        <v>12.20183184594</v>
+      </c>
+      <c r="J43" s="2">
+        <v>25.0928600036</v>
+      </c>
+      <c r="K43" s="2">
+        <v>22.42320788326</v>
+      </c>
+      <c r="L43" s="2">
+        <v>21.68908279446</v>
+      </c>
+      <c r="M43" s="2">
+        <v>33.50503297642</v>
+      </c>
+      <c r="N43" s="2">
+        <v>63.303523691509994</v>
+      </c>
+      <c r="O43" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P43" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="2">
+        <v>33.73517576958</v>
+      </c>
+      <c r="E44" s="2">
+        <v>26.35143918493</v>
+      </c>
+      <c r="F44" s="2">
+        <v>17.614930431790004</v>
+      </c>
+      <c r="G44" s="2">
+        <v>2.23739730874</v>
+      </c>
+      <c r="H44" s="2">
+        <v>27.1517293101</v>
+      </c>
+      <c r="I44" s="2">
+        <v>13.378545873679998</v>
+      </c>
+      <c r="J44" s="2">
+        <v>59.14283738457999</v>
+      </c>
+      <c r="K44" s="2">
+        <v>73.41488645519</v>
+      </c>
+      <c r="L44" s="2">
+        <v>30.729063688900002</v>
+      </c>
+      <c r="M44" s="2">
+        <v>-8.622230384179998</v>
+      </c>
+      <c r="N44" s="2">
+        <v>33.571045147410004</v>
+      </c>
+      <c r="O44" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P44" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="2">
+        <v>-1.6928834696300001</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.3002209890800001</v>
+      </c>
+      <c r="F45" s="2">
+        <v>6.5965283140499995</v>
+      </c>
+      <c r="G45" s="2">
+        <v>-1.5322582769299997</v>
+      </c>
+      <c r="H45" s="2">
+        <v>-9.54425857643</v>
+      </c>
+      <c r="I45" s="2">
+        <v>-7.53791010395</v>
+      </c>
+      <c r="J45" s="2">
+        <v>7.90470578596</v>
+      </c>
+      <c r="K45" s="2">
+        <v>-3.5561536686</v>
+      </c>
+      <c r="L45" s="2">
+        <v>2.44485287279</v>
+      </c>
+      <c r="M45" s="2">
+        <v>2.42465763871</v>
+      </c>
+      <c r="N45" s="2">
+        <v>5.60992124404</v>
+      </c>
+      <c r="O45" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P45" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="2">
+        <v>54.96628553302</v>
+      </c>
+      <c r="E46" s="2">
+        <v>46.78341560193999</v>
+      </c>
+      <c r="F46" s="2">
+        <v>35.63266327066</v>
+      </c>
+      <c r="G46" s="2">
+        <v>110.6249672618</v>
+      </c>
+      <c r="H46" s="2">
+        <v>87.21029406612999</v>
+      </c>
+      <c r="I46" s="2">
+        <v>78.93909152345</v>
+      </c>
+      <c r="J46" s="2">
+        <v>-16.22407717744</v>
+      </c>
+      <c r="K46" s="2">
+        <v>3.0867453701699996</v>
+      </c>
+      <c r="L46" s="2">
+        <v>-34.32228047012</v>
+      </c>
+      <c r="M46" s="2">
+        <v>9.436696139090001</v>
+      </c>
+      <c r="N46" s="2">
+        <v>-26.744025113050004</v>
+      </c>
+      <c r="O46" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P46" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="2">
+        <v>-3.8250130781200022</v>
+      </c>
+      <c r="E47" s="2">
+        <v>-22.137274710470003</v>
+      </c>
+      <c r="F47" s="2">
+        <v>60.81846387724</v>
+      </c>
+      <c r="G47" s="2">
+        <v>74.37158924772</v>
+      </c>
+      <c r="H47" s="2">
+        <v>152.10124648900998</v>
+      </c>
+      <c r="I47" s="2">
+        <v>-12.335287074400002</v>
+      </c>
+      <c r="J47" s="2">
+        <v>-16.64412491485</v>
+      </c>
+      <c r="K47" s="2">
+        <v>-99.63490470746</v>
+      </c>
+      <c r="L47" s="2">
+        <v>-12.154073569279998</v>
+      </c>
+      <c r="M47" s="2">
+        <v>-25.143314594199996</v>
+      </c>
+      <c r="N47" s="2">
+        <v>15.16471361704</v>
+      </c>
+      <c r="O47" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P47" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="2">
+        <v>-59.0</v>
+      </c>
+      <c r="E48" s="2">
+        <v>22.2</v>
+      </c>
+      <c r="F48" s="2">
+        <v>-31.200221713749997</v>
+      </c>
+      <c r="G48" s="2">
+        <v>68.31628322378</v>
+      </c>
+      <c r="H48" s="2">
+        <v>4.1624371448</v>
+      </c>
+      <c r="I48" s="2">
+        <v>56.923296446170006</v>
+      </c>
+      <c r="J48" s="2">
+        <v>-24.436936303410004</v>
+      </c>
+      <c r="K48" s="2">
+        <v>14.327536249790002</v>
+      </c>
+      <c r="L48" s="2">
+        <v>-26.519782399199997</v>
+      </c>
+      <c r="M48" s="2">
+        <v>37.16967926756</v>
+      </c>
+      <c r="N48" s="2">
+        <v>7.428925227530002</v>
+      </c>
+      <c r="O48" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P48" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="2">
+        <v>16.83943585908</v>
+      </c>
+      <c r="E49" s="2">
+        <v>-2.4315454620400003</v>
+      </c>
+      <c r="F49" s="2">
+        <v>14.95285426206</v>
+      </c>
+      <c r="G49" s="2">
+        <v>2.7969333749</v>
+      </c>
+      <c r="H49" s="2">
+        <v>33.766372004919994</v>
+      </c>
+      <c r="I49" s="2">
+        <v>18.93395140464</v>
+      </c>
+      <c r="J49" s="2">
+        <v>7.626702388890001</v>
+      </c>
+      <c r="K49" s="2">
+        <v>-23.889551951120005</v>
+      </c>
+      <c r="L49" s="2">
+        <v>21.409716682280003</v>
+      </c>
+      <c r="M49" s="2">
+        <v>-13.982295509219998</v>
+      </c>
+      <c r="N49" s="2">
+        <v>11.72390986629</v>
+      </c>
+      <c r="O49" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P49" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2.4017488012499997</v>
+      </c>
+      <c r="E50" s="2">
+        <v>-21.69259653685</v>
+      </c>
+      <c r="F50" s="2">
+        <v>-6.044511000000003</v>
+      </c>
+      <c r="G50" s="2">
+        <v>34.895008000000004</v>
+      </c>
+      <c r="H50" s="2">
+        <v>84.66334599999999</v>
+      </c>
+      <c r="I50" s="2">
+        <v>103.562636</v>
+      </c>
+      <c r="J50" s="2">
+        <v>20.351</v>
+      </c>
+      <c r="K50" s="2">
+        <v>76.08467</v>
+      </c>
+      <c r="L50" s="2">
+        <v>35.36789</v>
+      </c>
+      <c r="M50" s="2">
+        <v>-30.54172</v>
+      </c>
+      <c r="N50" s="2">
+        <v>-4.486459999999999</v>
+      </c>
+      <c r="O50" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P50" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="2">
+        <v>115.03497988612997</v>
+      </c>
+      <c r="E51" s="2">
+        <v>144.00566360015</v>
+      </c>
+      <c r="F51" s="2">
+        <v>220.70640722274</v>
+      </c>
+      <c r="G51" s="2">
+        <v>454.4782246684</v>
+      </c>
+      <c r="H51" s="2">
+        <v>536.5913536903399</v>
+      </c>
+      <c r="I51" s="2">
+        <v>358.31397597507004</v>
+      </c>
+      <c r="J51" s="2">
+        <v>158.82451252062</v>
+      </c>
+      <c r="K51" s="2">
+        <v>176.29505103697002</v>
+      </c>
+      <c r="L51" s="2">
+        <v>127.19555040431999</v>
+      </c>
+      <c r="M51" s="2">
+        <v>100.99687471092001</v>
+      </c>
+      <c r="N51" s="2">
+        <v>214.43631911153</v>
+      </c>
+      <c r="O51" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P51" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" s="2">
+        <v>6.5716753710299995</v>
+      </c>
+      <c r="E52" s="2">
+        <v>6.56902666054</v>
+      </c>
+      <c r="F52" s="2">
+        <v>5.855692964199999</v>
+      </c>
+      <c r="G52" s="2">
+        <v>5.26697463935</v>
+      </c>
+      <c r="H52" s="2">
+        <v>8.75503296985</v>
+      </c>
+      <c r="I52" s="2">
+        <v>8.4837014696</v>
+      </c>
+      <c r="J52" s="2">
+        <v>6.34703796123</v>
+      </c>
+      <c r="K52" s="2">
+        <v>8.18521175701</v>
+      </c>
+      <c r="L52" s="2">
+        <v>5.5987854306900005</v>
+      </c>
+      <c r="M52" s="2">
+        <v>8.27978134612</v>
+      </c>
+      <c r="N52" s="2">
+        <v>9.56549690308</v>
+      </c>
+      <c r="O52" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P52" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2.3465288448400003</v>
+      </c>
+      <c r="E53" s="2">
+        <v>-0.16701981384000003</v>
+      </c>
+      <c r="F53" s="2">
+        <v>-0.54196502676</v>
+      </c>
+      <c r="G53" s="2">
+        <v>1.22336121063</v>
+      </c>
+      <c r="H53" s="2">
+        <v>0.88535169439</v>
+      </c>
+      <c r="I53" s="2">
+        <v>1.80401519306</v>
+      </c>
+      <c r="J53" s="2">
+        <v>0.89741956913</v>
+      </c>
+      <c r="K53" s="2">
+        <v>0.27615010866</v>
+      </c>
+      <c r="L53" s="2">
+        <v>0.43507584994000004</v>
+      </c>
+      <c r="M53" s="2">
+        <v>-0.00139981800999999</v>
+      </c>
+      <c r="N53" s="2">
+        <v>0.13983000285</v>
+      </c>
+      <c r="O53" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P53" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="I54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="J54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P54" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="2">
+        <v>10.86836261699</v>
+      </c>
+      <c r="E55" s="2">
+        <v>14.33129012266</v>
+      </c>
+      <c r="F55" s="2">
+        <v>13.09219496743</v>
+      </c>
+      <c r="G55" s="2">
+        <v>7.7540600479599995</v>
+      </c>
+      <c r="H55" s="2">
+        <v>9.76983288677</v>
+      </c>
+      <c r="I55" s="2">
+        <v>12.55813772336</v>
+      </c>
+      <c r="J55" s="2">
+        <v>15.06045700294</v>
+      </c>
+      <c r="K55" s="2">
+        <v>13.2629324873</v>
+      </c>
+      <c r="L55" s="2">
+        <v>12.068250713000001</v>
+      </c>
+      <c r="M55" s="2">
+        <v>15.26587844133</v>
+      </c>
+      <c r="N55" s="2">
+        <v>18.94644560053</v>
+      </c>
+      <c r="O55" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P55" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" s="2">
+        <v>19.97338438318</v>
+      </c>
+      <c r="E56" s="2">
+        <v>25.15046448624</v>
+      </c>
+      <c r="F56" s="2">
+        <v>22.499066653039996</v>
+      </c>
+      <c r="G56" s="2">
+        <v>19.55978364868</v>
+      </c>
+      <c r="H56" s="2">
+        <v>20.59936158645</v>
+      </c>
+      <c r="I56" s="2">
+        <v>20.37247494356</v>
+      </c>
+      <c r="J56" s="2">
+        <v>26.36027973996</v>
+      </c>
+      <c r="K56" s="2">
+        <v>26.009821190020002</v>
+      </c>
+      <c r="L56" s="2">
+        <v>34.17318215271</v>
+      </c>
+      <c r="M56" s="2">
+        <v>36.58053169348</v>
+      </c>
+      <c r="N56" s="2">
+        <v>40.079038677599996</v>
+      </c>
+      <c r="O56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P56" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="2">
+        <v>-0.38662468136</v>
+      </c>
+      <c r="E57" s="2">
+        <v>-0.1576955691</v>
+      </c>
+      <c r="F57" s="2">
+        <v>-0.3313127579</v>
+      </c>
+      <c r="G57" s="2">
+        <v>-0.22872131352999997</v>
+      </c>
+      <c r="H57" s="2">
+        <v>-0.36506476983</v>
+      </c>
+      <c r="I57" s="2">
+        <v>-0.13698924623</v>
+      </c>
+      <c r="J57" s="2">
+        <v>-0.20069680748999996</v>
+      </c>
+      <c r="K57" s="2">
+        <v>-0.35231599065</v>
+      </c>
+      <c r="L57" s="2">
+        <v>0.024573607440000002</v>
+      </c>
+      <c r="M57" s="2">
+        <v>2.9436474665300003</v>
+      </c>
+      <c r="N57" s="2">
+        <v>1.06888447357</v>
+      </c>
+      <c r="O57" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P57" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G58" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H58" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="I58" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="J58" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K58" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L58" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M58" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N58" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O58" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P58" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="2">
+        <v>12.068017164009998</v>
+      </c>
+      <c r="E59" s="2">
+        <v>3.2849305006500007</v>
+      </c>
+      <c r="F59" s="2">
+        <v>12.05998023515</v>
+      </c>
+      <c r="G59" s="2">
+        <v>7.989977168039999</v>
+      </c>
+      <c r="H59" s="2">
+        <v>11.49681029267</v>
+      </c>
+      <c r="I59" s="2">
+        <v>11.674036958530001</v>
+      </c>
+      <c r="J59" s="2">
+        <v>14.6450239014</v>
+      </c>
+      <c r="K59" s="2">
+        <v>11.969303777000002</v>
+      </c>
+      <c r="L59" s="2">
+        <v>10.75366024023</v>
+      </c>
+      <c r="M59" s="2">
+        <v>14.549067234209998</v>
+      </c>
+      <c r="N59" s="2">
+        <v>10.860087396359999</v>
+      </c>
+      <c r="O59" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P59" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" s="2">
+        <v>28.146485521889996</v>
+      </c>
+      <c r="E60" s="2">
+        <v>26.71971636309</v>
+      </c>
+      <c r="F60" s="2">
+        <v>38.64056826033</v>
+      </c>
+      <c r="G60" s="2">
+        <v>64.05115701506</v>
+      </c>
+      <c r="H60" s="2">
+        <v>35.259276328140004</v>
+      </c>
+      <c r="I60" s="2">
+        <v>31.65416552933</v>
+      </c>
+      <c r="J60" s="2">
+        <v>-11.42820518796</v>
+      </c>
+      <c r="K60" s="2">
+        <v>-19.309948406609998</v>
+      </c>
+      <c r="L60" s="2">
+        <v>30.01100582937</v>
+      </c>
+      <c r="M60" s="2">
+        <v>8.516749824369999</v>
+      </c>
+      <c r="N60" s="2">
+        <v>35.97958363227</v>
+      </c>
+      <c r="O60" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P60" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" s="2">
+        <v>79.58782922057999</v>
+      </c>
+      <c r="E61" s="2">
+        <v>75.73071275024</v>
+      </c>
+      <c r="F61" s="2">
+        <v>91.27422529549</v>
+      </c>
+      <c r="G61" s="2">
+        <v>105.61659241618999</v>
+      </c>
+      <c r="H61" s="2">
+        <v>86.40060098844</v>
+      </c>
+      <c r="I61" s="2">
+        <v>86.40954257120998</v>
+      </c>
+      <c r="J61" s="2">
+        <v>51.68131617921001</v>
+      </c>
+      <c r="K61" s="2">
+        <v>40.04115492273001</v>
+      </c>
+      <c r="L61" s="2">
+        <v>93.06453382338</v>
+      </c>
+      <c r="M61" s="2">
+        <v>86.13425618802998</v>
+      </c>
+      <c r="N61" s="2">
+        <v>116.63936668626</v>
+      </c>
+      <c r="O61" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P61" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" s="2">
+        <v>222.06112803532</v>
+      </c>
+      <c r="E62" s="2">
+        <v>267.90221396505996</v>
+      </c>
+      <c r="F62" s="2">
+        <v>234.798709293</v>
+      </c>
+      <c r="G62" s="2">
+        <v>343.11492308751</v>
+      </c>
+      <c r="H62" s="2">
+        <v>406.04722571649</v>
+      </c>
+      <c r="I62" s="2">
+        <v>374.60946718831997</v>
+      </c>
+      <c r="J62" s="2">
+        <v>385.36516335565</v>
+      </c>
+      <c r="K62" s="2">
+        <v>250.29826830045</v>
+      </c>
+      <c r="L62" s="2">
+        <v>249.73720280285</v>
+      </c>
+      <c r="M62" s="2">
+        <v>201.98710778640998</v>
+      </c>
+      <c r="N62" s="2">
+        <v>200.76355026046</v>
+      </c>
+      <c r="O62" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P62" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D63" s="2">
+        <v>34.2725871352033</v>
+      </c>
+      <c r="E63" s="2">
+        <v>39.1059723499086</v>
+      </c>
+      <c r="F63" s="2">
+        <v>-38.667607773339796</v>
+      </c>
+      <c r="G63" s="2">
+        <v>77.74807540110761</v>
+      </c>
+      <c r="H63" s="2">
+        <v>21.4346675283671</v>
+      </c>
+      <c r="I63" s="2">
+        <v>37.156120852800704</v>
+      </c>
+      <c r="J63" s="2">
+        <v>-36.551507106326</v>
+      </c>
+      <c r="K63" s="2">
+        <v>42.1900044065786</v>
+      </c>
+      <c r="L63" s="2">
+        <v>59.0829709721476</v>
+      </c>
+      <c r="M63" s="2">
+        <v>-13.711692797037</v>
+      </c>
+      <c r="N63" s="2">
+        <v>31.1561559604735</v>
+      </c>
+      <c r="O63" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P63" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D64" s="2">
+        <v>96.0827547650467</v>
+      </c>
+      <c r="E64" s="2">
+        <v>68.5773532765314</v>
+      </c>
+      <c r="F64" s="2">
+        <v>46.130239122909806</v>
+      </c>
+      <c r="G64" s="2">
+        <v>156.0571483089324</v>
+      </c>
+      <c r="H64" s="2">
+        <v>123.1226820143629</v>
+      </c>
+      <c r="I64" s="2">
+        <v>77.3398975385093</v>
+      </c>
+      <c r="J64" s="2">
+        <v>-79.07895274976401</v>
+      </c>
+      <c r="K64" s="2">
+        <v>-51.2049807891986</v>
+      </c>
+      <c r="L64" s="2">
+        <v>-18.645037195197595</v>
+      </c>
+      <c r="M64" s="2">
+        <v>72.33453797464699</v>
+      </c>
+      <c r="N64" s="2">
+        <v>105.9821702802265</v>
+      </c>
+      <c r="O64" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P64" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D65" s="2">
+        <v>-31.561485001679998</v>
+      </c>
+      <c r="E65" s="2">
+        <v>-26.254346702860005</v>
+      </c>
+      <c r="F65" s="2">
+        <v>-38.21601534512</v>
+      </c>
+      <c r="G65" s="2">
+        <v>-28.18154280869</v>
+      </c>
+      <c r="H65" s="2">
+        <v>-53.80554918098</v>
+      </c>
+      <c r="I65" s="2">
+        <v>-28.491162263299998</v>
+      </c>
+      <c r="J65" s="2">
+        <v>-45.406818480389994</v>
+      </c>
+      <c r="K65" s="2">
+        <v>-55.98667259834</v>
+      </c>
+      <c r="L65" s="2">
+        <v>-22.18131884308</v>
+      </c>
+      <c r="M65" s="2">
+        <v>-51.59824874909</v>
+      </c>
+      <c r="N65" s="2">
+        <v>-53.600197005530006</v>
+      </c>
+      <c r="O65" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P65" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D66" s="2">
+        <v>-70.712597818185</v>
+      </c>
+      <c r="E66" s="2">
+        <v>71.419407656445</v>
+      </c>
+      <c r="F66" s="2">
+        <v>122.4236378218</v>
+      </c>
+      <c r="G66" s="2">
+        <v>127.42700683375499</v>
+      </c>
+      <c r="H66" s="2">
+        <v>165.83058110474</v>
+      </c>
+      <c r="I66" s="2">
+        <v>65.67098124022999</v>
+      </c>
+      <c r="J66" s="2">
+        <v>29.298294292574994</v>
+      </c>
+      <c r="K66" s="2">
+        <v>-76.87153709603001</v>
+      </c>
+      <c r="L66" s="2">
+        <v>-18.48988851937501</v>
+      </c>
+      <c r="M66" s="2">
+        <v>44.89062664962</v>
+      </c>
+      <c r="N66" s="2">
+        <v>40.32321386697</v>
+      </c>
+      <c r="O66" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P66" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D67" s="2">
+        <v>88.5752171033937</v>
+      </c>
+      <c r="E67" s="2">
+        <v>1.8178210197663018</v>
+      </c>
+      <c r="F67" s="2">
+        <v>115.8747421439132</v>
+      </c>
+      <c r="G67" s="2">
+        <v>-43.3516641148827</v>
+      </c>
+      <c r="H67" s="2">
+        <v>79.6951306735718</v>
+      </c>
+      <c r="I67" s="2">
+        <v>9.184315412214797</v>
+      </c>
+      <c r="J67" s="2">
+        <v>64.4956431894631</v>
+      </c>
+      <c r="K67" s="2">
+        <v>-34.67871785278481</v>
+      </c>
+      <c r="L67" s="2">
+        <v>11.063133531017698</v>
+      </c>
+      <c r="M67" s="2">
+        <v>12.8671551507938</v>
+      </c>
+      <c r="N67" s="2">
+        <v>57.5512737618284</v>
+      </c>
+      <c r="O67" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P67" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" s="2">
+        <v>-41.73271388699229</v>
+      </c>
+      <c r="E68" s="2">
+        <v>18.8545906784623</v>
+      </c>
+      <c r="F68" s="2">
+        <v>-29.740668804142793</v>
+      </c>
+      <c r="G68" s="2">
+        <v>56.593807937863296</v>
+      </c>
+      <c r="H68" s="2">
+        <v>21.8702724494778</v>
+      </c>
+      <c r="I68" s="2">
+        <v>47.098420837900804</v>
+      </c>
+      <c r="J68" s="2">
+        <v>3.9717282396450986</v>
+      </c>
+      <c r="K68" s="2">
+        <v>-11.220287771570801</v>
+      </c>
+      <c r="L68" s="2">
+        <v>-58.821617573088304</v>
+      </c>
+      <c r="M68" s="2">
+        <v>21.4843184521998</v>
+      </c>
+      <c r="N68" s="2">
+        <v>-25.553307851763602</v>
+      </c>
+      <c r="O68" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P68" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D69" s="2">
+        <v>34.7799716532036</v>
+      </c>
+      <c r="E69" s="2">
+        <v>-3.6020702909435984</v>
+      </c>
+      <c r="F69" s="2">
+        <v>69.9420577598196</v>
+      </c>
+      <c r="G69" s="2">
+        <v>-6.882372996935602</v>
+      </c>
+      <c r="H69" s="2">
+        <v>46.8352942474604</v>
+      </c>
+      <c r="I69" s="2">
+        <v>82.3423016727644</v>
+      </c>
+      <c r="J69" s="2">
+        <v>70.0621648190068</v>
+      </c>
+      <c r="K69" s="2">
+        <v>-18.024970350904404</v>
+      </c>
+      <c r="L69" s="2">
+        <v>36.240638475825605</v>
+      </c>
+      <c r="M69" s="2">
+        <v>12.6588889165664</v>
+      </c>
+      <c r="N69" s="2">
+        <v>71.2618110655752</v>
+      </c>
+      <c r="O69" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P69" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D70" s="2">
+        <v>331.76486198531</v>
+      </c>
+      <c r="E70" s="2">
+        <v>437.82094195236994</v>
+      </c>
+      <c r="F70" s="2">
+        <v>482.54509421883995</v>
+      </c>
+      <c r="G70" s="2">
+        <v>682.52538164866</v>
+      </c>
+      <c r="H70" s="2">
+        <v>811.03030455349</v>
+      </c>
+      <c r="I70" s="2">
+        <v>664.9103424794399</v>
+      </c>
+      <c r="J70" s="2">
+        <v>392.15571555986</v>
+      </c>
+      <c r="K70" s="2">
+        <v>44.501106248199974</v>
+      </c>
+      <c r="L70" s="2">
+        <v>237.9860836511</v>
+      </c>
+      <c r="M70" s="2">
+        <v>300.91269338410996</v>
+      </c>
+      <c r="N70" s="2">
+        <v>427.88467033823997</v>
+      </c>
+      <c r="O70" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P70" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D71" s="2">
+        <v>61.25905705630999</v>
+      </c>
+      <c r="E71" s="2">
+        <v>120.76667692928999</v>
+      </c>
+      <c r="F71" s="2">
+        <v>97.72779640186</v>
+      </c>
+      <c r="G71" s="2">
+        <v>115.33419689413999</v>
+      </c>
+      <c r="H71" s="2">
+        <v>168.66097145897</v>
+      </c>
+      <c r="I71" s="2">
+        <v>133.39269501657</v>
+      </c>
+      <c r="J71" s="2">
+        <v>161.70026254795002</v>
+      </c>
+      <c r="K71" s="2">
+        <v>145.88916637821</v>
+      </c>
+      <c r="L71" s="2">
+        <v>159.86037342243</v>
+      </c>
+      <c r="M71" s="2">
+        <v>148.06364797049</v>
+      </c>
+      <c r="N71" s="2">
+        <v>151.75474359141998</v>
+      </c>
+      <c r="O71" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P71" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D72" s="2">
+        <v>12.172120462623301</v>
+      </c>
+      <c r="E72" s="2">
+        <v>2.7832120091285995</v>
+      </c>
+      <c r="F72" s="2">
+        <v>-42.5088481501698</v>
+      </c>
+      <c r="G72" s="2">
+        <v>-2.9730693097924</v>
+      </c>
+      <c r="H72" s="2">
+        <v>-22.886196687892898</v>
+      </c>
+      <c r="I72" s="2">
+        <v>-6.1817808774593</v>
+      </c>
+      <c r="J72" s="2">
+        <v>-27.631702137195997</v>
+      </c>
+      <c r="K72" s="2">
+        <v>0.4545620941785984</v>
+      </c>
+      <c r="L72" s="2">
+        <v>18.6309612952676</v>
+      </c>
+      <c r="M72" s="2">
+        <v>2.358701845823001</v>
+      </c>
+      <c r="N72" s="2">
+        <v>33.9460802115235</v>
+      </c>
+      <c r="O72" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P72" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D73" s="2">
+        <v>17.9685680141967</v>
+      </c>
+      <c r="E73" s="2">
+        <v>-0.38587388421860047</v>
+      </c>
+      <c r="F73" s="2">
+        <v>12.2907690228098</v>
+      </c>
+      <c r="G73" s="2">
+        <v>7.066751974462401</v>
+      </c>
+      <c r="H73" s="2">
+        <v>50.68496086180289</v>
+      </c>
+      <c r="I73" s="2">
+        <v>31.7176000357593</v>
+      </c>
+      <c r="J73" s="2">
+        <v>16.424356163246</v>
+      </c>
+      <c r="K73" s="2">
+        <v>13.752376471771399</v>
+      </c>
+      <c r="L73" s="2">
+        <v>18.5993166270624</v>
+      </c>
+      <c r="M73" s="2">
+        <v>16.389969338797002</v>
+      </c>
+      <c r="N73" s="2">
+        <v>13.0595408026965</v>
+      </c>
+      <c r="O73" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P73" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D74" s="2">
+        <v>-39.51675558221</v>
+      </c>
+      <c r="E74" s="2">
+        <v>-36.18804823961</v>
+      </c>
+      <c r="F74" s="2">
+        <v>-46.47136129685</v>
+      </c>
+      <c r="G74" s="2">
+        <v>-26.412491221639996</v>
+      </c>
+      <c r="H74" s="2">
+        <v>-51.593310538560004</v>
+      </c>
+      <c r="I74" s="2">
+        <v>-31.497582766369998</v>
+      </c>
+      <c r="J74" s="2">
+        <v>-44.53191630827</v>
+      </c>
+      <c r="K74" s="2">
+        <v>-59.522376618639996</v>
+      </c>
+      <c r="L74" s="2">
+        <v>-25.51027709429</v>
+      </c>
+      <c r="M74" s="2">
+        <v>-54.681608640600004</v>
+      </c>
+      <c r="N74" s="2">
+        <v>-60.637720389420004</v>
+      </c>
+      <c r="O74" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P74" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D75" s="2">
+        <v>-53.610757438565</v>
+      </c>
+      <c r="E75" s="2">
+        <v>48.721143547415</v>
+      </c>
+      <c r="F75" s="2">
+        <v>49.4337568182</v>
+      </c>
+      <c r="G75" s="2">
+        <v>61.39215926133499</v>
+      </c>
+      <c r="H75" s="2">
+        <v>46.332667810109996</v>
+      </c>
+      <c r="I75" s="2">
+        <v>60.9053857787</v>
+      </c>
+      <c r="J75" s="2">
+        <v>-5.032552234175002</v>
+      </c>
+      <c r="K75" s="2">
+        <v>-61.900191618280004</v>
+      </c>
+      <c r="L75" s="2">
+        <v>-72.485451773655</v>
+      </c>
+      <c r="M75" s="2">
+        <v>32.562415407239996</v>
+      </c>
+      <c r="N75" s="2">
+        <v>-6.3679958007999975</v>
+      </c>
+      <c r="O75" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P75" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D76" s="2">
+        <v>20.8752856739337</v>
+      </c>
+      <c r="E76" s="2">
+        <v>3.4499882013863</v>
+      </c>
+      <c r="F76" s="2">
+        <v>76.4509271499232</v>
+      </c>
+      <c r="G76" s="2">
+        <v>4.109181587997302</v>
+      </c>
+      <c r="H76" s="2">
+        <v>41.1892862992818</v>
+      </c>
+      <c r="I76" s="2">
+        <v>14.0524473200548</v>
+      </c>
+      <c r="J76" s="2">
+        <v>63.5905831609331</v>
+      </c>
+      <c r="K76" s="2">
+        <v>-48.420995136434804</v>
+      </c>
+      <c r="L76" s="2">
+        <v>0.5504979773877023</v>
+      </c>
+      <c r="M76" s="2">
+        <v>15.447996358393798</v>
+      </c>
+      <c r="N76" s="2">
+        <v>38.243462797138406</v>
+      </c>
+      <c r="O76" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P76" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D77" s="2">
+        <v>1.4633396616577004</v>
+      </c>
+      <c r="E77" s="2">
+        <v>4.0288737689623</v>
+      </c>
+      <c r="F77" s="2">
+        <v>12.404465743507199</v>
+      </c>
+      <c r="G77" s="2">
+        <v>8.1375062416133</v>
+      </c>
+      <c r="H77" s="2">
+        <v>2.0044693804978</v>
+      </c>
+      <c r="I77" s="2">
+        <v>15.440025684720801</v>
+      </c>
+      <c r="J77" s="2">
+        <v>4.5518740205551</v>
+      </c>
+      <c r="K77" s="2">
+        <v>1.8026323912092</v>
+      </c>
+      <c r="L77" s="2">
+        <v>-8.6214691452283</v>
+      </c>
+      <c r="M77" s="2">
+        <v>-2.9252624423402</v>
+      </c>
+      <c r="N77" s="2">
+        <v>-2.8656965644735997</v>
+      </c>
+      <c r="O77" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P77" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D78" s="2">
+        <v>19.7905273540636</v>
+      </c>
+      <c r="E78" s="2">
+        <v>-7.348646902433599</v>
+      </c>
+      <c r="F78" s="2">
+        <v>24.506330228699603</v>
+      </c>
+      <c r="G78" s="2">
+        <v>-5.062824334115601</v>
+      </c>
+      <c r="H78" s="2">
+        <v>5.795883871200401</v>
+      </c>
+      <c r="I78" s="2">
+        <v>7.744141956534401</v>
+      </c>
+      <c r="J78" s="2">
+        <v>24.7980942227668</v>
+      </c>
+      <c r="K78" s="2">
+        <v>-15.619511110884401</v>
+      </c>
+      <c r="L78" s="2">
+        <v>1.4818657001355997</v>
+      </c>
+      <c r="M78" s="2">
+        <v>-7.4841119912436</v>
+      </c>
+      <c r="N78" s="2">
+        <v>10.019796780475199</v>
+      </c>
+      <c r="O78" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P78" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D79" s="2">
+        <v>40.401385202009976</v>
+      </c>
+      <c r="E79" s="2">
+        <v>135.82732542992</v>
+      </c>
+      <c r="F79" s="2">
+        <v>183.83383591798</v>
+      </c>
+      <c r="G79" s="2">
+        <v>161.59141109399997</v>
+      </c>
+      <c r="H79" s="2">
+        <v>240.18873245540993</v>
+      </c>
+      <c r="I79" s="2">
+        <v>225.57293214851</v>
+      </c>
+      <c r="J79" s="2">
+        <v>193.86899943581003</v>
+      </c>
+      <c r="K79" s="2">
+        <v>-23.564337148870003</v>
+      </c>
+      <c r="L79" s="2">
+        <v>92.50581700911</v>
+      </c>
+      <c r="M79" s="2">
+        <v>149.73174784656</v>
+      </c>
+      <c r="N79" s="2">
+        <v>177.15221142855998</v>
+      </c>
+      <c r="O79" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P79" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D80" s="2">
+        <v>34.65663088614</v>
+      </c>
+      <c r="E80" s="2">
+        <v>29.81734863517</v>
+      </c>
+      <c r="F80" s="2">
+        <v>24.7546562601</v>
+      </c>
+      <c r="G80" s="2">
+        <v>16.80741378021</v>
+      </c>
+      <c r="H80" s="2">
+        <v>37.81474341273</v>
+      </c>
+      <c r="I80" s="2">
+        <v>46.676455267639994</v>
+      </c>
+      <c r="J80" s="2">
+        <v>41.9758277351</v>
+      </c>
+      <c r="K80" s="2">
+        <v>37.00125138658</v>
+      </c>
+      <c r="L80" s="2">
+        <v>32.313528310609996</v>
+      </c>
+      <c r="M80" s="2">
+        <v>31.82333061417</v>
+      </c>
+      <c r="N80" s="2">
+        <v>32.945612772909996</v>
+      </c>
+      <c r="O80" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P80" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D81" s="2">
+        <v>3.70728777277</v>
+      </c>
+      <c r="E81" s="2">
+        <v>-3.9541357421999996</v>
+      </c>
+      <c r="F81" s="2">
+        <v>-13.84003094669</v>
+      </c>
+      <c r="G81" s="2">
+        <v>-6.568713314229999</v>
+      </c>
+      <c r="H81" s="2">
+        <v>-2.80642931843</v>
+      </c>
+      <c r="I81" s="2">
+        <v>2.5735016061</v>
+      </c>
+      <c r="J81" s="2">
+        <v>7.886984598369999</v>
+      </c>
+      <c r="K81" s="2">
+        <v>2.8827374983800005</v>
+      </c>
+      <c r="L81" s="2">
+        <v>-2.76104695892</v>
+      </c>
+      <c r="M81" s="2">
+        <v>-1.75119188596</v>
+      </c>
+      <c r="N81" s="2">
+        <v>-0.18997587229000001</v>
+      </c>
+      <c r="O81" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P81" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D82" s="2">
+        <v>14.895935555369999</v>
+      </c>
+      <c r="E82" s="2">
+        <v>14.40907544244</v>
+      </c>
+      <c r="F82" s="2">
+        <v>9.16662929312</v>
+      </c>
+      <c r="G82" s="2">
+        <v>18.68761247898</v>
+      </c>
+      <c r="H82" s="2">
+        <v>22.965830126380002</v>
+      </c>
+      <c r="I82" s="2">
+        <v>-0.18915931709999967</v>
+      </c>
+      <c r="J82" s="2">
+        <v>-8.36170425706</v>
+      </c>
+      <c r="K82" s="2">
+        <v>-3.70044867894</v>
+      </c>
+      <c r="L82" s="2">
+        <v>0.5377045998000005</v>
+      </c>
+      <c r="M82" s="2">
+        <v>1.4535673449200002</v>
+      </c>
+      <c r="N82" s="2">
+        <v>8.72914022947</v>
+      </c>
+      <c r="O82" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P82" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D83" s="2">
+        <v>-3.53034321781</v>
+      </c>
+      <c r="E83" s="2">
+        <v>-2.68450386368</v>
+      </c>
+      <c r="F83" s="2">
+        <v>-4.271906123180001</v>
+      </c>
+      <c r="G83" s="2">
+        <v>-3.9835519550800003</v>
+      </c>
+      <c r="H83" s="2">
+        <v>-4.57126838569</v>
+      </c>
+      <c r="I83" s="2">
+        <v>-4.21254493408</v>
+      </c>
+      <c r="J83" s="2">
+        <v>-5.1773774128</v>
+      </c>
+      <c r="K83" s="2">
+        <v>-6.16412904916</v>
+      </c>
+      <c r="L83" s="2">
+        <v>-5.20267529735</v>
+      </c>
+      <c r="M83" s="2">
+        <v>-5.644219676249999</v>
+      </c>
+      <c r="N83" s="2">
+        <v>-5.65140783148</v>
+      </c>
+      <c r="O83" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P83" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D84" s="2">
+        <v>-1.21465708163</v>
+      </c>
+      <c r="E84" s="2">
+        <v>6.30354023482</v>
+      </c>
+      <c r="F84" s="2">
+        <v>1.47558007381</v>
+      </c>
+      <c r="G84" s="2">
+        <v>-7.52465715196</v>
+      </c>
+      <c r="H84" s="2">
+        <v>4.006420167039998</v>
+      </c>
+      <c r="I84" s="2">
+        <v>5.178280239919999</v>
+      </c>
+      <c r="J84" s="2">
+        <v>10.14385677844</v>
+      </c>
+      <c r="K84" s="2">
+        <v>2.804541579179999</v>
+      </c>
+      <c r="L84" s="2">
+        <v>-2.30015358285</v>
+      </c>
+      <c r="M84" s="2">
+        <v>2.7350508138</v>
+      </c>
+      <c r="N84" s="2">
+        <v>-0.9352488415199995</v>
+      </c>
+      <c r="O84" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P84" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D85" s="2">
+        <v>1.8532628951799994</v>
+      </c>
+      <c r="E85" s="2">
+        <v>13.18037668</v>
+      </c>
+      <c r="F85" s="2">
+        <v>6.96374039481</v>
+      </c>
+      <c r="G85" s="2">
+        <v>17.16257611105</v>
+      </c>
+      <c r="H85" s="2">
+        <v>-4.5489532939499995</v>
+      </c>
+      <c r="I85" s="2">
+        <v>5.16820320552</v>
+      </c>
+      <c r="J85" s="2">
+        <v>1.83223295282</v>
+      </c>
+      <c r="K85" s="2">
+        <v>10.02124834005</v>
+      </c>
+      <c r="L85" s="2">
+        <v>-0.6784458625100004</v>
+      </c>
+      <c r="M85" s="2">
+        <v>10.49554872502</v>
+      </c>
+      <c r="N85" s="2">
+        <v>-0.6023691628100005</v>
+      </c>
+      <c r="O85" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P85" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D86" s="2">
+        <v>0.18362652287000003</v>
+      </c>
+      <c r="E86" s="2">
+        <v>-0.67933357605</v>
+      </c>
+      <c r="F86" s="2">
+        <v>-1.33562128848</v>
+      </c>
+      <c r="G86" s="2">
+        <v>1.22444744752</v>
+      </c>
+      <c r="H86" s="2">
+        <v>3.87245137789</v>
+      </c>
+      <c r="I86" s="2">
+        <v>2.83366463383</v>
+      </c>
+      <c r="J86" s="2">
+        <v>7.532873630559999</v>
+      </c>
+      <c r="K86" s="2">
+        <v>-2.97032953359</v>
+      </c>
+      <c r="L86" s="2">
+        <v>-0.77352942313</v>
+      </c>
+      <c r="M86" s="2">
+        <v>-0.7193783743999997</v>
+      </c>
+      <c r="N86" s="2">
+        <v>-0.10711468079999992</v>
+      </c>
+      <c r="O86" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P86" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D87" s="2">
+        <v>1.9961347542199999</v>
+      </c>
+      <c r="E87" s="2">
+        <v>-1.09436645705</v>
+      </c>
+      <c r="F87" s="2">
+        <v>1.65978026901</v>
+      </c>
+      <c r="G87" s="2">
+        <v>-0.6773685327</v>
+      </c>
+      <c r="H87" s="2">
+        <v>-0.07013232461999994</v>
+      </c>
+      <c r="I87" s="2">
+        <v>19.3673297635</v>
+      </c>
+      <c r="J87" s="2">
+        <v>3.11849202441</v>
+      </c>
+      <c r="K87" s="2">
+        <v>0.8088726877399999</v>
+      </c>
+      <c r="L87" s="2">
+        <v>0.2425726983000001</v>
+      </c>
+      <c r="M87" s="2">
+        <v>1.8000995782200002</v>
+      </c>
+      <c r="N87" s="2">
+        <v>1.76161308209</v>
+      </c>
+      <c r="O87" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P87" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D88" s="2">
+        <v>52.54787808710999</v>
+      </c>
+      <c r="E88" s="2">
+        <v>55.29800135345</v>
+      </c>
+      <c r="F88" s="2">
+        <v>24.572827932499997</v>
+      </c>
+      <c r="G88" s="2">
+        <v>35.12775886379001</v>
+      </c>
+      <c r="H88" s="2">
+        <v>56.66266176135</v>
+      </c>
+      <c r="I88" s="2">
+        <v>77.39573046532999</v>
+      </c>
+      <c r="J88" s="2">
+        <v>58.95118604984</v>
+      </c>
+      <c r="K88" s="2">
+        <v>40.683744230239995</v>
+      </c>
+      <c r="L88" s="2">
+        <v>21.377954483949996</v>
+      </c>
+      <c r="M88" s="2">
+        <v>40.192807139520006</v>
+      </c>
+      <c r="N88" s="2">
+        <v>35.95024969557</v>
+      </c>
+      <c r="O88" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P88" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D89" s="2">
+        <v>2.99887756441</v>
+      </c>
+      <c r="E89" s="2">
+        <v>2.68428121071</v>
+      </c>
+      <c r="F89" s="2">
+        <v>3.27653049338</v>
+      </c>
+      <c r="G89" s="2">
+        <v>2.55505749787</v>
+      </c>
+      <c r="H89" s="2">
+        <v>2.5620590960500005</v>
+      </c>
+      <c r="I89" s="2">
+        <v>2.7475140274900003</v>
+      </c>
+      <c r="J89" s="2">
+        <v>3.20183662212</v>
+      </c>
+      <c r="K89" s="2">
+        <v>5.75103948936</v>
+      </c>
+      <c r="L89" s="2">
+        <v>3.76050929581</v>
+      </c>
+      <c r="M89" s="2">
+        <v>5.096258038109999</v>
+      </c>
+      <c r="N89" s="2">
+        <v>2.56548886324</v>
+      </c>
+      <c r="O89" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P89" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0.008926565210000001</v>
+      </c>
+      <c r="E90" s="2">
+        <v>-0.013417095379999997</v>
+      </c>
+      <c r="F90" s="2">
+        <v>-0.10334287298</v>
+      </c>
+      <c r="G90" s="2">
+        <v>-0.11431584985</v>
+      </c>
+      <c r="H90" s="2">
+        <v>-0.13266194763</v>
+      </c>
+      <c r="I90" s="2">
+        <v>-0.09982903884</v>
+      </c>
+      <c r="J90" s="2">
+        <v>0.14622509031999997</v>
+      </c>
+      <c r="K90" s="2">
+        <v>0.007454533229999999</v>
+      </c>
+      <c r="L90" s="2">
+        <v>0.05221530452</v>
+      </c>
+      <c r="M90" s="2">
+        <v>-0.03156674081</v>
+      </c>
+      <c r="N90" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O90" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P90" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D91" s="2">
+        <v>2.9201805878200005</v>
+      </c>
+      <c r="E91" s="2">
+        <v>-0.60333641513</v>
+      </c>
+      <c r="F91" s="2">
+        <v>-0.81713278374</v>
+      </c>
+      <c r="G91" s="2">
+        <v>-1.58610106704</v>
+      </c>
+      <c r="H91" s="2">
+        <v>-0.75784023898</v>
+      </c>
+      <c r="I91" s="2">
+        <v>-0.8704247304000001</v>
+      </c>
+      <c r="J91" s="2">
+        <v>-0.15709208739000005</v>
+      </c>
+      <c r="K91" s="2">
+        <v>0.16001802469000004</v>
+      </c>
+      <c r="L91" s="2">
+        <v>0.8575471277500001</v>
+      </c>
+      <c r="M91" s="2">
+        <v>-0.79123846085</v>
+      </c>
+      <c r="N91" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O91" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P91" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D92" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F92" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G92" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H92" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="I92" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="J92" s="2">
+        <v>-2.0527900000000014E-5</v>
+      </c>
+      <c r="K92" s="2">
+        <v>6.7156713E-4</v>
+      </c>
+      <c r="L92" s="2">
+        <v>-5.4555049E-4</v>
+      </c>
+      <c r="M92" s="2">
+        <v>-3.20108E-5</v>
+      </c>
+      <c r="N92" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O92" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P92" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D93" s="2">
+        <v>0.16887354808000002</v>
+      </c>
+      <c r="E93" s="2">
+        <v>1.44613832072</v>
+      </c>
+      <c r="F93" s="2">
+        <v>-0.21700576530000004</v>
+      </c>
+      <c r="G93" s="2">
+        <v>0.5751139538</v>
+      </c>
+      <c r="H93" s="2">
+        <v>0.36688926984000003</v>
+      </c>
+      <c r="I93" s="2">
+        <v>4.5714808828099995</v>
+      </c>
+      <c r="J93" s="2">
+        <v>-0.12185039705</v>
+      </c>
+      <c r="K93" s="2">
+        <v>-0.28540105905</v>
+      </c>
+      <c r="L93" s="2">
+        <v>-0.17983783836</v>
+      </c>
+      <c r="M93" s="2">
+        <v>-0.20467779035000006</v>
+      </c>
+      <c r="N93" s="2">
+        <v>0.71080182877</v>
+      </c>
+      <c r="O93" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P93" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D94" s="2">
+        <v>-0.61425009312</v>
+      </c>
+      <c r="E94" s="2">
+        <v>3.34401959288</v>
+      </c>
+      <c r="F94" s="2">
+        <v>3.1663005575800005</v>
+      </c>
+      <c r="G94" s="2">
+        <v>3.28528605073</v>
+      </c>
+      <c r="H94" s="2">
+        <v>0.7350868213600001</v>
+      </c>
+      <c r="I94" s="2">
+        <v>0.3903625464899998</v>
+      </c>
+      <c r="J94" s="2">
+        <v>2.215469518</v>
+      </c>
+      <c r="K94" s="2">
+        <v>0.33628016587000004</v>
+      </c>
+      <c r="L94" s="2">
+        <v>0.6278688585499999</v>
+      </c>
+      <c r="M94" s="2">
+        <v>0.36756855792</v>
+      </c>
+      <c r="N94" s="2">
+        <v>-1.2698189715800003</v>
+      </c>
+      <c r="O94" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P94" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D95" s="2">
+        <v>-0.037607287560000036</v>
+      </c>
+      <c r="E95" s="2">
+        <v>-0.52885652555</v>
+      </c>
+      <c r="F95" s="2">
+        <v>0.4660353518</v>
+      </c>
+      <c r="G95" s="2">
+        <v>0.9236718770699999</v>
+      </c>
+      <c r="H95" s="2">
+        <v>0.44138495696999996</v>
+      </c>
+      <c r="I95" s="2">
+        <v>0.06173930681000006</v>
+      </c>
+      <c r="J95" s="2">
+        <v>0.4699892998700001</v>
+      </c>
+      <c r="K95" s="2">
+        <v>-1.00482926405</v>
+      </c>
+      <c r="L95" s="2">
+        <v>0.039048436019999966</v>
+      </c>
+      <c r="M95" s="2">
+        <v>0.6408748412699999</v>
+      </c>
+      <c r="N95" s="2">
+        <v>0.52944449767</v>
+      </c>
+      <c r="O95" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P95" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D96" s="2">
+        <v>-0.043880790210000006</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0.0711046278</v>
+      </c>
+      <c r="F96" s="2">
+        <v>-0.43619551652</v>
+      </c>
+      <c r="G96" s="2">
+        <v>-0.18370479147999996</v>
+      </c>
+      <c r="H96" s="2">
+        <v>0.14864654712</v>
+      </c>
+      <c r="I96" s="2">
+        <v>1.5282719778499998</v>
+      </c>
+      <c r="J96" s="2">
+        <v>1.3818414718200003</v>
+      </c>
+      <c r="K96" s="2">
+        <v>0.10920803628999999</v>
+      </c>
+      <c r="L96" s="2">
+        <v>-0.012026384459999996</v>
+      </c>
+      <c r="M96" s="2">
+        <v>0.2350927419</v>
+      </c>
+      <c r="N96" s="2">
+        <v>-7.582920399999992E-4</v>
+      </c>
+      <c r="O96" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P96" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D97" s="2">
+        <v>5.40112009463</v>
+      </c>
+      <c r="E97" s="2">
+        <v>6.399933716049999</v>
+      </c>
+      <c r="F97" s="2">
+        <v>5.335189464220002</v>
+      </c>
+      <c r="G97" s="2">
+        <v>5.455007671100001</v>
+      </c>
+      <c r="H97" s="2">
+        <v>3.363564504730001</v>
+      </c>
+      <c r="I97" s="2">
+        <v>8.329114972210002</v>
+      </c>
+      <c r="J97" s="2">
+        <v>7.13639898979</v>
+      </c>
+      <c r="K97" s="2">
+        <v>5.074441493470001</v>
+      </c>
+      <c r="L97" s="2">
+        <v>5.14477924934</v>
+      </c>
+      <c r="M97" s="2">
+        <v>5.31227917639</v>
+      </c>
+      <c r="N97" s="2">
+        <v>2.5351579260599997</v>
+      </c>
+      <c r="O97" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P97" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D98" s="2">
+        <v>96.16247193624001</v>
+      </c>
+      <c r="E98" s="2">
+        <v>91.00735042852</v>
+      </c>
+      <c r="F98" s="2">
+        <v>91.74883183323999</v>
+      </c>
+      <c r="G98" s="2">
+        <v>161.34678422534</v>
+      </c>
+      <c r="H98" s="2">
+        <v>174.02178467371002</v>
+      </c>
+      <c r="I98" s="2">
+        <v>170.05319238877</v>
+      </c>
+      <c r="J98" s="2">
+        <v>144.97124873907</v>
+      </c>
+      <c r="K98" s="2">
+        <v>45.232540353439994</v>
+      </c>
+      <c r="L98" s="2">
+        <v>37.12140107231</v>
+      </c>
+      <c r="M98" s="2">
+        <v>5.606278334929999</v>
+      </c>
+      <c r="N98" s="2">
+        <v>-4.665894434879999</v>
+      </c>
+      <c r="O98" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P98" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D99" s="2">
+        <v>7.274498124049998</v>
+      </c>
+      <c r="E99" s="2">
+        <v>37.63155099204</v>
+      </c>
+      <c r="F99" s="2">
+        <v>19.57950130315</v>
+      </c>
+      <c r="G99" s="2">
+        <v>60.755232241250006</v>
+      </c>
+      <c r="H99" s="2">
+        <v>38.56184734234</v>
+      </c>
+      <c r="I99" s="2">
+        <v>44.3389996183</v>
+      </c>
+      <c r="J99" s="2">
+        <v>11.158969394580001</v>
+      </c>
+      <c r="K99" s="2">
+        <v>27.30535555434</v>
+      </c>
+      <c r="L99" s="2">
+        <v>31.99425496605</v>
+      </c>
+      <c r="M99" s="2">
+        <v>-24.5481432074</v>
+      </c>
+      <c r="N99" s="2">
+        <v>-2.94939837876</v>
+      </c>
+      <c r="O99" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P99" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" s="2">
+        <v>54.782727293410005</v>
+      </c>
+      <c r="E100" s="2">
+        <v>47.67771893516</v>
+      </c>
+      <c r="F100" s="2">
+        <v>37.340214051740006</v>
+      </c>
+      <c r="G100" s="2">
+        <v>129.09959605806</v>
+      </c>
+      <c r="H100" s="2">
+        <v>50.36013854269</v>
+      </c>
+      <c r="I100" s="2">
+        <v>43.36724570532</v>
+      </c>
+      <c r="J100" s="2">
+        <v>-86.14865651271</v>
+      </c>
+      <c r="K100" s="2">
+        <v>-61.29560529856</v>
+      </c>
+      <c r="L100" s="2">
+        <v>-41.97472827652</v>
+      </c>
+      <c r="M100" s="2">
+        <v>48.58545523065</v>
+      </c>
+      <c r="N100" s="2">
+        <v>72.06656282696</v>
+      </c>
+      <c r="O100" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P100" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" s="2">
+        <v>-1.6428251977500001</v>
+      </c>
+      <c r="E101" s="2">
+        <v>-2.1047929574</v>
+      </c>
+      <c r="F101" s="2">
+        <v>-2.36612791578</v>
+      </c>
+      <c r="G101" s="2">
+        <v>-3.39084465078</v>
+      </c>
+      <c r="H101" s="2">
+        <v>-3.84718843861</v>
+      </c>
+      <c r="I101" s="2">
+        <v>-2.99818330575</v>
+      </c>
+      <c r="J101" s="2">
+        <v>-5.59305509069</v>
+      </c>
+      <c r="K101" s="2">
+        <v>-3.2630466775499998</v>
+      </c>
+      <c r="L101" s="2">
+        <v>-0.14231156566999995</v>
+      </c>
+      <c r="M101" s="2">
+        <v>-2.52363728685</v>
+      </c>
+      <c r="N101" s="2">
+        <v>0.5099840318700003</v>
+      </c>
+      <c r="O101" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P101" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D102" s="2">
+        <v>-42.8172939943</v>
+      </c>
+      <c r="E102" s="2">
+        <v>-12.91696497319</v>
+      </c>
+      <c r="F102" s="2">
+        <v>44.12150981543</v>
+      </c>
+      <c r="G102" s="2">
+        <v>48.11526205652</v>
+      </c>
+      <c r="H102" s="2">
+        <v>92.34834941595001</v>
+      </c>
+      <c r="I102" s="2">
+        <v>-26.042999808330002</v>
+      </c>
+      <c r="J102" s="2">
+        <v>-1.4915790181399997</v>
+      </c>
+      <c r="K102" s="2">
+        <v>-48.41209992206</v>
+      </c>
+      <c r="L102" s="2">
+        <v>16.266027642209995</v>
+      </c>
+      <c r="M102" s="2">
+        <v>-34.0365273281</v>
+      </c>
+      <c r="N102" s="2">
+        <v>-3.6271801670599997</v>
+      </c>
+      <c r="O102" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P102" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D103" s="2">
+        <v>61.90371282573</v>
+      </c>
+      <c r="E103" s="2">
+        <v>-19.36394159667</v>
+      </c>
+      <c r="F103" s="2">
+        <v>23.2430966133</v>
+      </c>
+      <c r="G103" s="2">
+        <v>-41.51270618289001</v>
+      </c>
+      <c r="H103" s="2">
+        <v>34.25453534608</v>
+      </c>
+      <c r="I103" s="2">
+        <v>-24.679357774190002</v>
+      </c>
+      <c r="J103" s="2">
+        <v>-21.66764217657</v>
+      </c>
+      <c r="K103" s="2">
+        <v>3.2680211076699996</v>
+      </c>
+      <c r="L103" s="2">
+        <v>-2.818156454170001</v>
+      </c>
+      <c r="M103" s="2">
+        <v>-26.40639021063</v>
+      </c>
+      <c r="N103" s="2">
+        <v>14.04973513368</v>
+      </c>
+      <c r="O103" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P103" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D104" s="2">
+        <v>-46.8</v>
+      </c>
+      <c r="E104" s="2">
+        <v>18.05</v>
+      </c>
+      <c r="F104" s="2">
+        <v>-40.07977958407999</v>
+      </c>
+      <c r="G104" s="2">
+        <v>47.89588617637</v>
+      </c>
+      <c r="H104" s="2">
+        <v>15.961084412669999</v>
+      </c>
+      <c r="I104" s="2">
+        <v>17.4156954382</v>
+      </c>
+      <c r="J104" s="2">
+        <v>-20.46776046302</v>
+      </c>
+      <c r="K104" s="2">
+        <v>-10.810042273630001</v>
+      </c>
+      <c r="L104" s="2">
+        <v>-44.18937508236</v>
+      </c>
+      <c r="M104" s="2">
+        <v>20.54630438131</v>
+      </c>
+      <c r="N104" s="2">
+        <v>-26.25099210755</v>
+      </c>
+      <c r="O104" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P104" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D105" s="2">
+        <v>4.38656251735</v>
+      </c>
+      <c r="E105" s="2">
+        <v>-6.100765844339999</v>
+      </c>
+      <c r="F105" s="2">
+        <v>23.10723749557</v>
+      </c>
+      <c r="G105" s="2">
+        <v>-13.816071807070001</v>
+      </c>
+      <c r="H105" s="2">
+        <v>20.31591964648</v>
+      </c>
+      <c r="I105" s="2">
+        <v>32.96046504793</v>
+      </c>
+      <c r="J105" s="2">
+        <v>28.00418641214</v>
+      </c>
+      <c r="K105" s="2">
+        <v>-19.428958238319996</v>
+      </c>
+      <c r="L105" s="2">
+        <v>19.34916128985</v>
+      </c>
+      <c r="M105" s="2">
+        <v>10.599324722290001</v>
+      </c>
+      <c r="N105" s="2">
+        <v>42.61708402735</v>
+      </c>
+      <c r="O105" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P105" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D106" s="2">
+        <v>133.24985350473003</v>
+      </c>
+      <c r="E106" s="2">
+        <v>153.88015498412</v>
+      </c>
+      <c r="F106" s="2">
+        <v>196.69448361257</v>
+      </c>
+      <c r="G106" s="2">
+        <v>388.49313811679997</v>
+      </c>
+      <c r="H106" s="2">
+        <v>421.97647094131</v>
+      </c>
+      <c r="I106" s="2">
+        <v>254.41505731024998</v>
+      </c>
+      <c r="J106" s="2">
+        <v>48.76571128466</v>
+      </c>
+      <c r="K106" s="2">
+        <v>-67.40383539467001</v>
+      </c>
+      <c r="L106" s="2">
+        <v>15.606273591699996</v>
+      </c>
+      <c r="M106" s="2">
+        <v>-2.177335363800001</v>
+      </c>
+      <c r="N106" s="2">
+        <v>91.74990093161</v>
+      </c>
+      <c r="O106" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P106" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D107" s="2">
+        <v>26.98409059222</v>
+      </c>
+      <c r="E107" s="2">
+        <v>23.626556761369997</v>
+      </c>
+      <c r="F107" s="2">
+        <v>17.29089430442</v>
+      </c>
+      <c r="G107" s="2">
+        <v>47.071470689950004</v>
+      </c>
+      <c r="H107" s="2">
+        <v>22.98766707503</v>
+      </c>
+      <c r="I107" s="2">
+        <v>21.73961048785</v>
+      </c>
+      <c r="J107" s="2">
+        <v>33.51598771140999</v>
+      </c>
+      <c r="K107" s="2">
+        <v>16.424270692860002</v>
+      </c>
+      <c r="L107" s="2">
+        <v>16.681390701690002</v>
+      </c>
+      <c r="M107" s="2">
+        <v>11.39759282871</v>
+      </c>
+      <c r="N107" s="2">
+        <v>18.16359946777</v>
+      </c>
+      <c r="O107" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P107" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D108" s="2">
+        <v>11.10975421055</v>
+      </c>
+      <c r="E108" s="2">
+        <v>2.65876218632</v>
+      </c>
+      <c r="F108" s="2">
+        <v>-1.7948871066499996</v>
+      </c>
+      <c r="G108" s="2">
+        <v>26.64894163373</v>
+      </c>
+      <c r="H108" s="2">
+        <v>8.69810813998</v>
+      </c>
+      <c r="I108" s="2">
+        <v>-3.4747704553</v>
+      </c>
+      <c r="J108" s="2">
+        <v>-28.1119840524</v>
+      </c>
+      <c r="K108" s="2">
+        <v>11.539894726450001</v>
+      </c>
+      <c r="L108" s="2">
+        <v>11.16658636523</v>
+      </c>
+      <c r="M108" s="2">
+        <v>10.26050719131</v>
+      </c>
+      <c r="N108" s="2">
+        <v>0.3494499999999999</v>
+      </c>
+      <c r="O108" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P108" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D109" s="2">
+        <v>5.51534331425</v>
+      </c>
+      <c r="E109" s="2">
+        <v>7.47976919828</v>
+      </c>
+      <c r="F109" s="2">
+        <v>-11.850240461019999</v>
+      </c>
+      <c r="G109" s="2">
+        <v>2.78928886447</v>
+      </c>
+      <c r="H109" s="2">
+        <v>-0.13040727752999998</v>
+      </c>
+      <c r="I109" s="2">
+        <v>3.31463584493</v>
+      </c>
+      <c r="J109" s="2">
+        <v>-0.8358560558500001</v>
+      </c>
+      <c r="K109" s="2">
+        <v>-0.12132130815999995</v>
+      </c>
+      <c r="L109" s="2">
+        <v>3.33512272671</v>
+      </c>
+      <c r="M109" s="2">
+        <v>6.69678452113</v>
+      </c>
+      <c r="N109" s="2">
+        <v>12.1269264211</v>
+      </c>
+      <c r="O109" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P109" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D110" s="2">
+        <v>13.12843899609</v>
+      </c>
+      <c r="E110" s="2">
+        <v>14.722998357829999</v>
+      </c>
+      <c r="F110" s="2">
+        <v>14.89337999069</v>
+      </c>
+      <c r="G110" s="2">
+        <v>5.60534501881</v>
+      </c>
+      <c r="H110" s="2">
+        <v>6.20621818188</v>
+      </c>
+      <c r="I110" s="2">
+        <v>10.217148742900001</v>
+      </c>
+      <c r="J110" s="2">
+        <v>9.89555085927</v>
+      </c>
+      <c r="K110" s="2">
+        <v>12.96220817988</v>
+      </c>
+      <c r="L110" s="2">
+        <v>8.67449066472</v>
+      </c>
+      <c r="M110" s="2">
+        <v>11.25124886541</v>
+      </c>
+      <c r="N110" s="2">
+        <v>12.1789471835</v>
+      </c>
+      <c r="O110" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P110" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" s="2">
+        <v>26.761237148230002</v>
+      </c>
+      <c r="E111" s="2">
+        <v>27.865550526680003</v>
+      </c>
+      <c r="F111" s="2">
+        <v>27.609796879659996</v>
+      </c>
+      <c r="G111" s="2">
+        <v>24.86912871406</v>
+      </c>
+      <c r="H111" s="2">
+        <v>22.7762544418</v>
+      </c>
+      <c r="I111" s="2">
+        <v>21.05883414713</v>
+      </c>
+      <c r="J111" s="2">
+        <v>25.8004191635</v>
+      </c>
+      <c r="K111" s="2">
+        <v>30.92161392418</v>
+      </c>
+      <c r="L111" s="2">
+        <v>40.20952703328</v>
+      </c>
+      <c r="M111" s="2">
+        <v>43.83436554703</v>
+      </c>
+      <c r="N111" s="2">
+        <v>50.54283684758</v>
+      </c>
+      <c r="O111" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P111" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D112" s="2">
+        <v>4.557205801670001</v>
+      </c>
+      <c r="E112" s="2">
+        <v>1.20737814217</v>
+      </c>
+      <c r="F112" s="2">
+        <v>6.050677428299999</v>
+      </c>
+      <c r="G112" s="2">
+        <v>-26.396001681770002</v>
+      </c>
+      <c r="H112" s="2">
+        <v>8.0651755008</v>
+      </c>
+      <c r="I112" s="2">
+        <v>14.252660114340001</v>
+      </c>
+      <c r="J112" s="2">
+        <v>18.52499973428</v>
+      </c>
+      <c r="K112" s="2">
+        <v>0.11672767005999958</v>
+      </c>
+      <c r="L112" s="2">
+        <v>13.381369011759999</v>
+      </c>
+      <c r="M112" s="2">
+        <v>12.96243172009</v>
+      </c>
+      <c r="N112" s="2">
+        <v>7.130263965399999</v>
+      </c>
+      <c r="O112" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P112" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D113" s="2">
+        <v>3.45792721604</v>
+      </c>
+      <c r="E113" s="2">
+        <v>-2.0160929889</v>
+      </c>
+      <c r="F113" s="2">
+        <v>-1.19576902689</v>
+      </c>
+      <c r="G113" s="2">
+        <v>-1.58770380471</v>
+      </c>
+      <c r="H113" s="2">
+        <v>-0.4091176785499999</v>
+      </c>
+      <c r="I113" s="2">
+        <v>11.347295774340001</v>
+      </c>
+      <c r="J113" s="2">
+        <v>11.88475175168</v>
+      </c>
+      <c r="K113" s="2">
+        <v>1.76228090849</v>
+      </c>
+      <c r="L113" s="2">
+        <v>-5.27629235839</v>
+      </c>
+      <c r="M113" s="2">
+        <v>3.9417800463600003</v>
+      </c>
+      <c r="N113" s="2">
+        <v>3.14105100339</v>
+      </c>
+      <c r="O113" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P113" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D114" s="2">
+        <v>8.650627817779998</v>
+      </c>
+      <c r="E114" s="2">
+        <v>10.870604285079999</v>
+      </c>
+      <c r="F114" s="2">
+        <v>21.104905283060003</v>
+      </c>
+      <c r="G114" s="2">
+        <v>12.857596468430001</v>
+      </c>
+      <c r="H114" s="2">
+        <v>20.644976507280003</v>
+      </c>
+      <c r="I114" s="2">
+        <v>20.74209292695</v>
+      </c>
+      <c r="J114" s="2">
+        <v>12.759550687870002</v>
+      </c>
+      <c r="K114" s="2">
+        <v>16.105418274269997</v>
+      </c>
+      <c r="L114" s="2">
+        <v>15.179065172</v>
+      </c>
+      <c r="M114" s="2">
+        <v>7.5084838654</v>
+      </c>
+      <c r="N114" s="2">
+        <v>16.8640754677</v>
+      </c>
+      <c r="O114" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P114" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D115" s="2">
+        <v>100.16462509683001</v>
+      </c>
+      <c r="E115" s="2">
+        <v>86.41552646883001</v>
+      </c>
+      <c r="F115" s="2">
+        <v>72.10875729157</v>
+      </c>
+      <c r="G115" s="2">
+        <v>91.85806590297</v>
+      </c>
+      <c r="H115" s="2">
+        <v>88.83887489069</v>
+      </c>
+      <c r="I115" s="2">
+        <v>99.19750758313998</v>
+      </c>
+      <c r="J115" s="2">
+        <v>83.43341979975999</v>
+      </c>
+      <c r="K115" s="2">
+        <v>89.71109306803</v>
+      </c>
+      <c r="L115" s="2">
+        <v>103.35125931699999</v>
+      </c>
+      <c r="M115" s="2">
+        <v>107.85319458544</v>
+      </c>
+      <c r="N115" s="2">
+        <v>120.49715035643999</v>
+      </c>
+      <c r="O115" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P115" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D116" s="2">
+        <v>178.35573000429</v>
+      </c>
+      <c r="E116" s="2">
+        <v>287.74218507841</v>
+      </c>
+      <c r="F116" s="2">
+        <v>242.10162730569002</v>
+      </c>
+      <c r="G116" s="2">
+        <v>517.21519649097</v>
+      </c>
+      <c r="H116" s="2">
+        <v>316.75759564682</v>
+      </c>
+      <c r="I116" s="2">
+        <v>415.7879772497</v>
+      </c>
+      <c r="J116" s="2">
+        <v>342.32561663499</v>
+      </c>
+      <c r="K116" s="2">
+        <v>348.47950216308004</v>
+      </c>
+      <c r="L116" s="2">
+        <v>305.62612196252</v>
+      </c>
+      <c r="M116" s="2">
+        <v>379.36921535506</v>
+      </c>
+      <c r="N116" s="2">
+        <v>350.59204652925</v>
+      </c>
+      <c r="O116" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P116" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D117" s="2">
+        <v>-70.25304578960001</v>
+      </c>
+      <c r="E117" s="2">
+        <v>-74.17075140839</v>
+      </c>
+      <c r="F117" s="2">
+        <v>-48.635108670070004</v>
+      </c>
+      <c r="G117" s="2">
+        <v>-43.73606384896999</v>
+      </c>
+      <c r="H117" s="2">
+        <v>-14.060979111649992</v>
+      </c>
+      <c r="I117" s="2">
+        <v>8.442623334790014</v>
+      </c>
+      <c r="J117" s="2">
+        <v>30.986046416279997</v>
+      </c>
+      <c r="K117" s="2">
+        <v>21.56612291831999</v>
+      </c>
+      <c r="L117" s="2">
+        <v>-22.32316689268</v>
+      </c>
+      <c r="M117" s="2">
+        <v>-37.22026172195</v>
+      </c>
+      <c r="N117" s="2">
+        <v>-38.56669910051998</v>
+      </c>
+      <c r="O117" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P117" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D118" s="2">
+        <v>-50.062974481759994</v>
+      </c>
+      <c r="E118" s="2">
+        <v>-94.52980944672001</v>
+      </c>
+      <c r="F118" s="2">
+        <v>-83.73776386162</v>
+      </c>
+      <c r="G118" s="2">
+        <v>-121.12830383743</v>
+      </c>
+      <c r="H118" s="2">
+        <v>-99.27371899046</v>
+      </c>
+      <c r="I118" s="2">
+        <v>-141.10446459709</v>
+      </c>
+      <c r="J118" s="2">
+        <v>-186.07939335324</v>
+      </c>
+      <c r="K118" s="2">
+        <v>-124.98888377395001</v>
+      </c>
+      <c r="L118" s="2">
+        <v>-124.71460808817001</v>
+      </c>
+      <c r="M118" s="2">
+        <v>-146.90143985789</v>
+      </c>
+      <c r="N118" s="2">
+        <v>-136.91104214033</v>
+      </c>
+      <c r="O118" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P118" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D119" s="2">
+        <v>62.67458599144</v>
+      </c>
+      <c r="E119" s="2">
+        <v>67.01169448639999</v>
+      </c>
+      <c r="F119" s="2">
+        <v>59.72125259323</v>
+      </c>
+      <c r="G119" s="2">
+        <v>74.58151669006</v>
+      </c>
+      <c r="H119" s="2">
+        <v>70.31260099987</v>
+      </c>
+      <c r="I119" s="2">
+        <v>76.77397377936</v>
+      </c>
+      <c r="J119" s="2">
+        <v>77.12166719342</v>
+      </c>
+      <c r="K119" s="2">
+        <v>90.83412284165</v>
+      </c>
+      <c r="L119" s="2">
+        <v>83.47031302693</v>
+      </c>
+      <c r="M119" s="2">
+        <v>92.43776210462</v>
+      </c>
+      <c r="N119" s="2">
+        <v>87.96475638753</v>
+      </c>
+      <c r="O119" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P119" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D120" s="2">
+        <v>120.71429572436998</v>
+      </c>
+      <c r="E120" s="2">
+        <v>186.05331870969997</v>
+      </c>
+      <c r="F120" s="2">
+        <v>169.45000736723003</v>
+      </c>
+      <c r="G120" s="2">
+        <v>426.93234549463006</v>
+      </c>
+      <c r="H120" s="2">
+        <v>273.73549854457997</v>
+      </c>
+      <c r="I120" s="2">
+        <v>359.90010976676007</v>
+      </c>
+      <c r="J120" s="2">
+        <v>264.35393689145</v>
+      </c>
+      <c r="K120" s="2">
+        <v>335.8908641491</v>
+      </c>
+      <c r="L120" s="2">
+        <v>242.05866000860001</v>
+      </c>
+      <c r="M120" s="2">
+        <v>287.68527587984</v>
+      </c>
+      <c r="N120" s="2">
+        <v>263.07906167593</v>
+      </c>
+      <c r="O120" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P120" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>